--- a/裁定工作表_v1.xlsx
+++ b/裁定工作表_v1.xlsx
@@ -54,7 +54,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,31 +62,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -464,12 +455,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>操作性定义</t>
         </is>
@@ -478,135 +469,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>分类总则</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>以手术经过 + 术中诊断为第一依据，现病史次之，出院诊断编码仅作参考。两名裁定者独立填写、互不查看，完成后计算 Cohen κ，分歧由第三方仲裁。</t>
+          <t>本表用途</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>总表，含机器初筛提示，仅供仲裁者参考，请勿在本表中裁定。两名裁定者分别在 裁定工作表_v1_裁定者A.xlsx 与 裁定工作表_v1_裁定者B.xlsx 中独立填写。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1 异物相关</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>术中或内镜证实消化道内异物，且穿孔部位与异物滞留/嵌顿部位一致。再按异物类型分磁性（磁珠、磁力珠、巴克球、磁铁）与非磁性（发卡、掏耳勺、电池等）；磁性者须在“磁性异物枚数”登记术中取出的确切枚数，记不清写 NR。</t>
+          <t>分类总则</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>以手术经过 + 术中诊断为第一依据，现病史次之，出院诊断编码仅作参考。两名裁定者独立填写、互不查看，完成后计算 Cohen κ，分歧由第三方仲裁。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2 新生儿自发性/胃壁肌层缺损</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>日龄≤28 天，术中见胃壁肌层缺损或胃壁自发破裂，无异物、无溃疡、无外伤与医源性操作史。</t>
+          <t>1 异物相关</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>术中或内镜证实消化道内异物，且穿孔部位与异物滞留/嵌顿部位一致。再按异物类型分磁性（磁珠、磁力珠、巴克球、磁铁）与非磁性（发卡、掏耳勺、电池等）；磁性者须在“磁性异物枚数”登记术中取出的确切枚数，记不清写 NR。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3 消化性溃疡</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>术中见慢性溃疡基底（胼胝样边缘、瘢痕化），或病理证实溃疡；含十二指肠球部溃疡穿孔。HP 状态另列登记。</t>
+          <t>2 新生儿自发性/胃壁肌层缺损</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>日龄≤28 天，术中见胃壁肌层缺损或胃壁自发破裂，无异物、无溃疡、无外伤与医源性操作史。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4 创伤</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>明确外力史（车祸、坠落、钝挫伤、虐待伤），术中见挫裂伤/系膜撕裂。</t>
+          <t>3 消化性溃疡</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>术中见慢性溃疡基底（胼胝样边缘、瘢痕化），或病理证实溃疡；含十二指肠球部溃疡穿孔。HP 状态另列登记。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5 医源性</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>穿孔发生于诊疗操作后且部位吻合：内镜操作、置管、既往手术吻合口/修补处漏。</t>
+          <t>4 创伤</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>明确外力史（车祸、坠落、钝挫伤、虐待伤），术中见挫裂伤/系膜撕裂。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6 其他/特发性</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>不符合以上任一条，或术中未能确定病因。包括先天畸形继发（十二指肠隔膜、环状胰腺）、NEC 累及、胃石、全身疾病背景下发生者，须在备注写明具体情形，后续按频次决定是否单列亚类。</t>
+          <t>5 医源性</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>穿孔发生于诊疗操作后且部位吻合：内镜操作、置管、既往手术吻合口/修补处漏。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>6 其他/特发性</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>不符合以上任一条，或术中未能确定病因。包括先天畸形继发（十二指肠隔膜、环状胰腺）、NEC 累及、胃石、全身疾病背景下发生者，须在备注写明具体情形，后续按频次决定是否单列亚类。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>9 排除</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>符合下列任一条即排除，并在“排除理由”写明具体条目：
 E1 穿孔部位不在胃或十二指肠（如单纯空/回肠、结肠、食管穿孔）；
 E2 本次住院并无活动性穿孔（如仅为溃疡、术后复查、拔管或造影随访）；
 E3 穿孔已在外院手术处理后转入我院，本次住院处理的是并发症；
-E4 同一患儿因同一次穿孔的再次住院——保留首次收治的那次住院，后续住院排除（其信息可回补到首次记录的并发症/再手术字段）。
+E4 同一患儿因同一次穿孔的再次住院——保留首次收治的那次住院，后续住院排除（其信息可回补到首次记录的并发症/再手术字段）；
+E5 病案资料严重缺失：已回 HIS 调阅原始病历（入院记录、手术记录、出院记录、影像及内镜报告）后，仍无法获得判定病因所需的任何依据。仅因科研平台导出缺少出院小结或手术记录者，不得直接按 E5 排除。
 注意：保守治疗成功者与家属拒绝手术者**不属于排除**，应正常纳入并在“手术入路”填“未手术”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>数据完整性标记</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>本列由脚本自动生成，标出无手术记录、无出院小结、非首次住院的病例。带标记者请优先裁定：它们既是排除条目 E2-E4 的高发人群，也可能是真实的非手术治疗病例，两者必须逐例读现病史区分，不得一律排除。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>穿孔部位</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>按穿孔的解剖位置填写，仅限胃 / 十二指肠 / 两者兼有。若同时存在空肠、回肠、结肠穿孔，另填“合并其他消化道穿孔”。</t>
+          <t>填写一致性</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>病因大类填“9排除”时，是否排除必须填“是”并选择排除理由，反之亦然；异物类型仅在病因大类为“1异物相关”时填磁性/非磁性，其余填 NA；磁性异物须填枚数（正整数，记不清写 NR）；纳入病例须填写穿孔部位、手术入路与结局。merge_adjudication.py 会逐条核查，不一致之处列入“逻辑核查”表退回本人修改。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>数据完整性标记</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>本列由脚本自动生成，标出无手术记录、无出院小结、非首次住院的病例。带标记者请优先裁定：它们既是排除条目 E2-E4 的高发人群，也可能是真实的非手术治疗病例，两者必须逐例读现病史区分，不得一律排除。标“无出院小结”“无手术记录”者先回 HIS 调阅原始病历，多为科研平台尚未同步，不等于病历缺失。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>穿孔部位</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>按穿孔的解剖位置填写，仅限胃 / 十二指肠 / 两者兼有。若同时存在空肠、回肠、结肠穿孔，另填“合并其他消化道穿孔”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>结局</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>“放弃治疗”指家属签字放弃后出院者，分析时与院内死亡合并为复合不良结局。</t>
         </is>
@@ -672,217 +688,217 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>科研患者编号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>科研就诊编号</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>住院号</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>第几次住院</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>数据完整性标记</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>性别</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>年龄_岁</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>年龄_天</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>年龄组</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>入院日期</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>入院年</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>住院天数</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>入院科别</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>门急诊诊断</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>主要出院诊断</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>全部出院诊断</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>术中诊断</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>手术名称</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>手术经过</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>手术日期</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>编码手术(全部)</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>主诉</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>现病史</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>既往史</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>出院情况</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>诊疗经过</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>机器初筛提示</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>磁性关键词命中</t>
         </is>
       </c>
-      <c r="AC1" s="5" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>病因大类</t>
         </is>
       </c>
-      <c r="AD1" s="5" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>异物类型</t>
         </is>
       </c>
-      <c r="AE1" s="5" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>磁性异物枚数</t>
         </is>
       </c>
-      <c r="AF1" s="5" t="inlineStr">
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>异物具体名称</t>
         </is>
       </c>
-      <c r="AG1" s="5" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>穿孔部位</t>
         </is>
       </c>
-      <c r="AH1" s="5" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>合并其他消化道穿孔</t>
         </is>
       </c>
-      <c r="AI1" s="5" t="inlineStr">
+      <c r="AI1" s="4" t="inlineStr">
         <is>
           <t>穿孔数目</t>
         </is>
       </c>
-      <c r="AJ1" s="5" t="inlineStr">
+      <c r="AJ1" s="4" t="inlineStr">
         <is>
           <t>手术入路</t>
         </is>
       </c>
-      <c r="AK1" s="5" t="inlineStr">
+      <c r="AK1" s="4" t="inlineStr">
         <is>
           <t>HP状态</t>
         </is>
       </c>
-      <c r="AL1" s="5" t="inlineStr">
+      <c r="AL1" s="4" t="inlineStr">
         <is>
           <t>结局</t>
         </is>
       </c>
-      <c r="AM1" s="5" t="inlineStr">
+      <c r="AM1" s="4" t="inlineStr">
         <is>
           <t>是否排除</t>
         </is>
       </c>
-      <c r="AN1" s="5" t="inlineStr">
+      <c r="AN1" s="4" t="inlineStr">
         <is>
           <t>排除理由</t>
         </is>
       </c>
-      <c r="AO1" s="5" t="inlineStr">
+      <c r="AO1" s="4" t="inlineStr">
         <is>
           <t>裁定者</t>
         </is>
       </c>
-      <c r="AP1" s="5" t="inlineStr">
+      <c r="AP1" s="4" t="inlineStr">
         <is>
           <t>裁定日期</t>
         </is>
       </c>
-      <c r="AQ1" s="5" t="inlineStr">
+      <c r="AQ1" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2229,86 +2245,86 @@
       <c r="AQ10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="5" t="n">
         <v>535638</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="5" t="n">
         <v>100650936</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="5" t="n">
         <v>1123666</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="n">
         <v>14.59</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="5" t="n">
         <v>5329</v>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>普外二病区</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>粘连性肠梗阻</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>粘连性肠梗阻</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>粘连性肠梗阻 | 胃穿孔</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr"/>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="6" t="inlineStr"/>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="6" t="inlineStr"/>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>胃穿孔修补术后12天，伴大便不排7天</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="W11" s="5" t="inlineStr">
         <is>
           <t>12天前患儿因胃穿孔在当地医院行手术治疗，术后2天有排便，术后5天拔除胃管后开始进食后患儿开始出现腹胀，腹痛，伴大便不排，不伴发热，予以重置胃管引流大量黄绿色胃液，腹痛腹胀缓解，仍无大便排出，复查CT提示小肠梗阻，当地医院建议转上级医院治疗，遂来我院，门诊以“肠梗阻”收入我科。患儿自发病以来，精神食欲睡眠一般，小便可，大便未排</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="X11" s="5" t="inlineStr">
         <is>
           <t>其它:无特殊
 传染病史:否认肝炎、结核或其他传染病史
@@ -2322,12 +2338,12 @@
 产伤史:无</t>
         </is>
       </c>
-      <c r="Y11" s="6" t="inlineStr">
+      <c r="Y11" s="5" t="inlineStr">
         <is>
           <t>出院时情况:患儿精神食欲睡眠良好，无发热，大便正常，小便正常。体检：神志清楚，反应可，心音有力，心律齐，呼吸平稳，双侧呼吸音清，腹部外形平坦，腹肌软，肠鸣音正常。伤口包扎好，敷料干燥。</t>
         </is>
       </c>
-      <c r="Z11" s="6" t="inlineStr">
+      <c r="Z11" s="5" t="inlineStr">
         <is>
           <t>杨**，男，14岁
 病例特点
@@ -2341,27 +2357,27 @@
     入院后完善相关检查，腹部立位片提示肠梗阻，行禁食，胃肠减压，抗感染、补液对症等治疗。今病情平稳，临床治愈，征得家长同意，办理出院。</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="inlineStr">
+      <c r="AA11" s="5" t="inlineStr">
         <is>
           <t>?6其他/待读</t>
         </is>
       </c>
-      <c r="AB11" s="6" t="inlineStr"/>
-      <c r="AC11" s="6" t="inlineStr"/>
-      <c r="AD11" s="6" t="inlineStr"/>
-      <c r="AE11" s="6" t="inlineStr"/>
-      <c r="AF11" s="6" t="inlineStr"/>
-      <c r="AG11" s="6" t="inlineStr"/>
-      <c r="AH11" s="6" t="inlineStr"/>
-      <c r="AI11" s="6" t="inlineStr"/>
-      <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="6" t="inlineStr"/>
-      <c r="AL11" s="6" t="inlineStr"/>
-      <c r="AM11" s="6" t="inlineStr"/>
-      <c r="AN11" s="6" t="inlineStr"/>
-      <c r="AO11" s="6" t="inlineStr"/>
-      <c r="AP11" s="6" t="inlineStr"/>
-      <c r="AQ11" s="6" t="inlineStr"/>
+      <c r="AB11" s="5" t="inlineStr"/>
+      <c r="AC11" s="5" t="inlineStr"/>
+      <c r="AD11" s="5" t="inlineStr"/>
+      <c r="AE11" s="5" t="inlineStr"/>
+      <c r="AF11" s="5" t="inlineStr"/>
+      <c r="AG11" s="5" t="inlineStr"/>
+      <c r="AH11" s="5" t="inlineStr"/>
+      <c r="AI11" s="5" t="inlineStr"/>
+      <c r="AJ11" s="5" t="inlineStr"/>
+      <c r="AK11" s="5" t="inlineStr"/>
+      <c r="AL11" s="5" t="inlineStr"/>
+      <c r="AM11" s="5" t="inlineStr"/>
+      <c r="AN11" s="5" t="inlineStr"/>
+      <c r="AO11" s="5" t="inlineStr"/>
+      <c r="AP11" s="5" t="inlineStr"/>
+      <c r="AQ11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3268,81 +3284,81 @@
       <c r="AQ17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="5" t="n">
         <v>1965377</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="5" t="n">
         <v>101078637</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="5" t="n">
         <v>1106946</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="5" t="n">
         <v>1.92</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="5" t="n">
         <v>702</v>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>3幼儿</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>2018-10-05</t>
         </is>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>普外二病区</t>
         </is>
       </c>
-      <c r="N18" s="6" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔</t>
         </is>
       </c>
-      <c r="O18" s="6" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔 | 低蛋白血症 | 代谢性酸中毒 | 腹腔间隔室综合征 | 多脏器损伤 | 心功能不全 | 凝血功能异常 | 腹部损伤 | 脓毒血症 | 感染性休克 | 急性化脓性弥漫性腹膜炎</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔；腹部损伤；急性化脓性弥漫性腹膜炎；脓毒血症；呼吸心跳骤停</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>小肠破裂修补术,空肠造口术,暂时性胃造口术,十二指肠造口术,开腹探查术,经皮腹部引流术</t>
         </is>
       </c>
-      <c r="S18" s="6" t="inlineStr">
+      <c r="S18" s="5" t="inlineStr">
         <is>
           <t>1、麻醉诱导后，成功气管插管，患儿心律逐渐下降，由170bpm降至90bpm，并持续下降，口唇及全身多处皮肤发绀，考虑呼吸心跳骤停可疑，立即予以心外按压呼吸机辅助呼吸等心肺复苏抢救处理，及时告知患儿家属患儿病情变化，患儿随时可能死亡。同时继续予以心肺复苏抢救治疗，心肺复苏成功，心律由40bpm升至140bpm并稳定140~160bpm之间。心肺复苏成功。予以冰枕降温保护颅脑。
 2、麻醉成功后取仰卧位，常规消毒，铺巾，上导尿管顺利。
@@ -3352,27 +3368,27 @@
 6、术泰舒冲洗创面及肠管表面未见明显出血，术泰舒冲洗腹腔，将肠管还纳腹腔后，于陶氏腔内置腹腔引流管一根，于十二指肠肠穿孔处留置腹腔引流管一根，另戳孔引出，吸净腹腔内积液后，留置透明质酸钠凝胶于腹腔预防粘连，腹膜切口下留置倍绫预防切口粘连，逐层关腹，间断缝合皮肤。外用手术止纱布后加压包扎。术毕置SICU。术中出血10ml，尿量50ml。</t>
         </is>
       </c>
-      <c r="T18" s="6" t="inlineStr">
+      <c r="T18" s="5" t="inlineStr">
         <is>
           <t>2018-10-05 00:00</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
+      <c r="U18" s="5" t="inlineStr">
         <is>
           <t>开腹探查术 | 小肠破裂修补术 | 空肠造口术 | 暂时性胃造口术 | 十二指肠造口术 | 近期开腹手术部位的再切开 | 呼吸机治疗[小于96小时] | 经皮腹部引流术</t>
         </is>
       </c>
-      <c r="V18" s="6" t="inlineStr">
+      <c r="V18" s="5" t="inlineStr">
         <is>
           <t>恶心、呕吐一天</t>
         </is>
       </c>
-      <c r="W18" s="6" t="inlineStr">
+      <c r="W18" s="5" t="inlineStr">
         <is>
           <t>1天前无明显诱因患儿出现恶心、呕吐一天，伴发热、腹痛，无尿频、尿急、尿痛及腰痛等不适。否认不洁饮食史，前日夜间曾有外伤史，在外院行检查，头部CT及脊柱CT无异常否认近期做过剧烈运动。否认在外院治疗。今来我院门诊就诊，以“腹痛”收入院。患儿自发病以来，精神食欲睡眠欠佳，小便量少，深黄，大便正常</t>
         </is>
       </c>
-      <c r="X18" s="6" t="inlineStr">
+      <c r="X18" s="5" t="inlineStr">
         <is>
           <t>其它:无特殊
 传染病史:否认肝炎、结核或其他传染病史
@@ -3386,29 +3402,29 @@
 产伤史:无</t>
         </is>
       </c>
-      <c r="Y18" s="6" t="inlineStr"/>
-      <c r="Z18" s="6" t="inlineStr"/>
-      <c r="AA18" s="6" t="inlineStr">
+      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="Z18" s="5" t="inlineStr"/>
+      <c r="AA18" s="5" t="inlineStr">
         <is>
           <t>?4创伤</t>
         </is>
       </c>
-      <c r="AB18" s="6" t="inlineStr"/>
-      <c r="AC18" s="6" t="inlineStr"/>
-      <c r="AD18" s="6" t="inlineStr"/>
-      <c r="AE18" s="6" t="inlineStr"/>
-      <c r="AF18" s="6" t="inlineStr"/>
-      <c r="AG18" s="6" t="inlineStr"/>
-      <c r="AH18" s="6" t="inlineStr"/>
-      <c r="AI18" s="6" t="inlineStr"/>
-      <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="6" t="inlineStr"/>
-      <c r="AL18" s="6" t="inlineStr"/>
-      <c r="AM18" s="6" t="inlineStr"/>
-      <c r="AN18" s="6" t="inlineStr"/>
-      <c r="AO18" s="6" t="inlineStr"/>
-      <c r="AP18" s="6" t="inlineStr"/>
-      <c r="AQ18" s="6" t="inlineStr"/>
+      <c r="AB18" s="5" t="inlineStr"/>
+      <c r="AC18" s="5" t="inlineStr"/>
+      <c r="AD18" s="5" t="inlineStr"/>
+      <c r="AE18" s="5" t="inlineStr"/>
+      <c r="AF18" s="5" t="inlineStr"/>
+      <c r="AG18" s="5" t="inlineStr"/>
+      <c r="AH18" s="5" t="inlineStr"/>
+      <c r="AI18" s="5" t="inlineStr"/>
+      <c r="AJ18" s="5" t="inlineStr"/>
+      <c r="AK18" s="5" t="inlineStr"/>
+      <c r="AL18" s="5" t="inlineStr"/>
+      <c r="AM18" s="5" t="inlineStr"/>
+      <c r="AN18" s="5" t="inlineStr"/>
+      <c r="AO18" s="5" t="inlineStr"/>
+      <c r="AP18" s="5" t="inlineStr"/>
+      <c r="AQ18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3706,81 +3722,81 @@
       <c r="AQ20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="5" t="n">
         <v>98278</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="5" t="n">
         <v>100213279</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="5" t="n">
         <v>1183756</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="5" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="5" t="n">
         <v>3488</v>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>2019-01-11</t>
         </is>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>重症医学科病区</t>
         </is>
       </c>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="O21" s="6" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>代谢性酸中毒 | 胃穿孔 | 腹腔感染 | 低血糖 | 弥漫性腹膜炎 | 脓毒性休克 | 肝功能异常 | 中度贫血 | 胸腔积液 | 心肌损害</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>胃穿孔，脓毒性休克，弥漫性腹膜炎</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>胃破裂修补术,肠粘连松解术,经皮腹部引流术,腹腔镜检查</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>１、平卧位，手术区域常规消毒铺巾；
 ２、脐环上侧、左、右侧经腹直肌切口、分别作5mm切口，常规建立ＣＯ２人工气腹，压力10mmHg，分别置入相应大小Ｔｒｏｃａ，内置腹腔镜目镜、无创血管钳或抓钳。探查腹膜见全腹肠管高度扩张充血，腹膜水肿充血，腹腔大量积液，约2000ml，为褐色浑浊液体，以双侧膈下为重，可见大量食物残渣；
@@ -3790,27 +3806,27 @@
 ５、术中出血约60ml，尿量约５0０ml。术中无标本。术中输注新鲜冰冻血浆400ml（编号：9000119013029，9000119016956）。</t>
         </is>
       </c>
-      <c r="T21" s="6" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>2019-01-11 00:00</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>肠粘连松解术 | 腹腔镜检查 | 经皮腹部引流术 | 胃破裂修补术 | 血浆置换 | 胃插管减压</t>
         </is>
       </c>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>反复呕吐胃内容物2天，腹痛半天</t>
         </is>
       </c>
-      <c r="W21" s="6" t="inlineStr">
+      <c r="W21" s="5" t="inlineStr">
         <is>
           <t>现病史:患儿2天前无明显诱因于晚餐后出现呕吐，为胃内容物及水样物，10余次/天，初无腹痛，无发热，无头晕、头痛，精神尚可，大便一日1次，外观正常，昨日就诊于当地卫生院，与哌拉西林2.25g及止吐药物治疗1天，具体不详，症状无改善，今晨04:30开始出现阵发性腹痛，较剧烈，逐渐加重，中间可缓解数分钟，今就诊与我院门诊，就诊过程中出现晕厥1次，急诊予补液等治疗，约1-2分钟后缓解，查腹盆CT提示消化道穿孔，急诊以“肠穿孔、休克”收入我科。发病以来，精神、食欲欠佳，睡眠一般，大便一日1次，小便尚可。</t>
         </is>
       </c>
-      <c r="X21" s="6" t="inlineStr">
+      <c r="X21" s="5" t="inlineStr">
         <is>
           <t>其它:无特殊
 传染病史:否认肝炎、结核或其他传染病史
@@ -3828,8 +3844,8 @@
 与CRE患者接触:否</t>
         </is>
       </c>
-      <c r="Y21" s="6" t="inlineStr"/>
-      <c r="Z21" s="6" t="inlineStr">
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="inlineStr">
         <is>
           <t>患儿魏**，男，9岁6月。
 病例特点
@@ -3847,27 +3863,27 @@
 【诊断证明已开；★请妥善保管此份出院记录、诊断证明及结账清单，出院10个工作日后(节假日除外)，病案科（内科楼3楼）复印报销所需其他资料；如需办理邮寄详询病案科复印处】</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
+      <c r="AA21" s="5" t="inlineStr">
         <is>
           <t>?6其他/待读</t>
         </is>
       </c>
-      <c r="AB21" s="6" t="inlineStr"/>
-      <c r="AC21" s="6" t="inlineStr"/>
-      <c r="AD21" s="6" t="inlineStr"/>
-      <c r="AE21" s="6" t="inlineStr"/>
-      <c r="AF21" s="6" t="inlineStr"/>
-      <c r="AG21" s="6" t="inlineStr"/>
-      <c r="AH21" s="6" t="inlineStr"/>
-      <c r="AI21" s="6" t="inlineStr"/>
-      <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="6" t="inlineStr"/>
-      <c r="AL21" s="6" t="inlineStr"/>
-      <c r="AM21" s="6" t="inlineStr"/>
-      <c r="AN21" s="6" t="inlineStr"/>
-      <c r="AO21" s="6" t="inlineStr"/>
-      <c r="AP21" s="6" t="inlineStr"/>
-      <c r="AQ21" s="6" t="inlineStr"/>
+      <c r="AB21" s="5" t="inlineStr"/>
+      <c r="AC21" s="5" t="inlineStr"/>
+      <c r="AD21" s="5" t="inlineStr"/>
+      <c r="AE21" s="5" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr"/>
+      <c r="AG21" s="5" t="inlineStr"/>
+      <c r="AH21" s="5" t="inlineStr"/>
+      <c r="AI21" s="5" t="inlineStr"/>
+      <c r="AJ21" s="5" t="inlineStr"/>
+      <c r="AK21" s="5" t="inlineStr"/>
+      <c r="AL21" s="5" t="inlineStr"/>
+      <c r="AM21" s="5" t="inlineStr"/>
+      <c r="AN21" s="5" t="inlineStr"/>
+      <c r="AO21" s="5" t="inlineStr"/>
+      <c r="AP21" s="5" t="inlineStr"/>
+      <c r="AQ21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6313,126 +6329,126 @@
       <c r="AQ38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="5" t="n">
         <v>1456895</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="5" t="n">
         <v>100475186</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C39" s="5" t="n">
         <v>2063109</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="5" t="n">
         <v>13.06</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="5" t="n">
         <v>4771</v>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>2021-04-09</t>
         </is>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="L39" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>普外二病区</t>
         </is>
       </c>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>腹痛(空腔脏器穿孔？)</t>
         </is>
       </c>
-      <c r="O39" s="6" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>消化性溃疡伴穿孔</t>
         </is>
       </c>
-      <c r="P39" s="6" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>幽门螺旋杆菌感染 | 消化性溃疡伴穿孔 | 腹腔感染</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr">
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="inlineStr">
         <is>
           <t>胃插管减压 | 全消化道造影</t>
         </is>
       </c>
-      <c r="V39" s="6" t="inlineStr">
+      <c r="V39" s="5" t="inlineStr">
         <is>
           <t>上腹疼痛伴呕吐1天</t>
         </is>
       </c>
-      <c r="W39" s="6" t="inlineStr">
+      <c r="W39" s="5" t="inlineStr">
         <is>
           <t>患儿昨日清晨突发腹痛，上腹疼痛，可耐受，昨晚疼痛加重，撕裂样疼痛，自行口服午时茶，呕吐两次，呕吐为进食物，不伴发热，无尿频、尿急、尿痛及腰痛等不适，疼痛无缓解一直至今，否认不洁饮食史，否认腹部外伤史，否认近期做过剧烈运动。今来我院门诊就诊，以“腹痛（空腔脏器破裂）”收入院。         患儿自发病以来，精神食欲睡眠欠佳，小便正常，大便未排。</t>
         </is>
       </c>
-      <c r="X39" s="6" t="inlineStr">
+      <c r="X39" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y39" s="6" t="inlineStr">
+      <c r="Y39" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神睡眠一般，食欲一般，无发热，大便基本正常，小便正常。查体：神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。</t>
         </is>
       </c>
-      <c r="Z39" s="6" t="inlineStr">
+      <c r="Z39" s="5" t="inlineStr">
         <is>
           <t>上腹疼痛伴呕吐1天，患者既往平时健康情况：一般，疾病史：有疾病史，胃病，外伤史：否认外伤史，过敏史：无，体温37.2℃，呼吸19次/分，规则，脉搏100次/分，规则，血压96/58mmHg，体重58Kg ，身长170cm，发育良好，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜巩膜无黄染，瞳孔等圆等大4mm，瞳孔对光反射正常，唇红润，扁桃体双侧无肿大，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率100次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，全腹腹肌紧张，有，上腹部剑突下疼痛压痛，不配合完成反跳痛，肝脏肋下未触及，胆囊Murphy征阴性，脾脏肋下未触及，未触及腹部包块，移动性浊音呈阴性，肠鸣音正常，无肾区叩痛，四肢正常，脊柱生理弯曲存在，无病理性畸形，病理反射无，Babinski征。，腹部平坦，未见胃肠型；触：腹部肌紧，剑突下压痛阳性，反跳痛查体不配合，未扪及包块；叩：移动性浊音阴性；听：肠鸣音正常，4次/分；双下肢无出血点。，2021-04-08梨园医院全腹ct提示右肝上少量游离气体，考虑空腔脏器破裂；2021-04-09我院腹平片提示未见游离气体，肠管少量积气，可见数个液平；我院2021-04-09血常规：WBC 11.09×10*9/L、N 80.7%、HGB 141g/L；，入院后完善相关检查，2021-04-09 腹盆CT平扫（含体层成像及三维重建）,胃窦部及十二直肠球部肠壁肿胀；胆汁淤积；右侧肾前筋膜增厚，肠管周围脂肪间隙模糊；盆腔积液；请结合临床。2021-04-09 血型测定(正反定型):ABO血型 A型，Rh(D)血型 阳性；2021-04-09 血浆凝血机制（4项）测定:凝血酶时间测定 17.7(s)，活化部分凝血活酶时间 33.8(s)，凝血酶原时间测定 15.2(s)↑，国际标准比率 1.33↑，纤维蛋白原检测 3.04(g/L)；2021-04-09 血清葡萄糖测定(血糖):葡萄糖 5.35(mmol/L)；2021-04-09 血清淀粉酶（AMY)测定:淀粉酶 30(U/L)；2021-04-09 血清肾功能5项（BUN、Cr、UA、Cys-C、RBP)测定:血液视黄醇结合蛋白 23.3(ug/ml)↓，Y-痕迹蛋白 0.84(mg/l)，尿素氮 6.00(mmol/L)，肌酐 69.0(μmol/L)↑，尿酸 486.0(μmol/L)↑；2021-04-09 血清肝功能11项测定:球蛋白 19.5(g/L)↓，白蛋白 46.5(g/L)，总蛋白 66.0(g/L)，直接胆红素 7.0(μmol/L)↑，总胆红素 38.5(μmol/L)↑，总胆汁酸 0.5(μmol/L)，白/球比值 2.4，碱性磷酸酶 156(U/L)，谷草转氨酶 7(U/L)↓，r-谷氨酰转肽酶 7(U/L)，胆碱酯酶 5395(U/L)，谷丙转氨酶 4(U/L)↓，前白蛋白 250.2(mg/l)；2021-04-09 血清电解质6项（K 、Na、Cl、Ca、Mg、P)测定:磷 1.31(mmol/L)，镁 0.89(mmol/L)，钾 4.11(mmol/L)，氯 104.9(mmol/L)，钠 142.4(mmol/L)，钙 2.33(mmol/L)；2021-04-09 艾滋病病毒抗体检测（化学发光法）:人类免疫缺陷病毒抗体 0.015(S/CO)；2021-04-09 梅毒特异抗体检测（荧光探针法）:梅毒螺旋体抗体 0.022(S/CO)；2021-04-09 血清丙肝抗体IgG(HCV-IgG)检测:丙肝抗体定量 0.032 [阴性(-)](COI)；2021-04-09 血清乙肝全套(五项）检测:乙肝核心抗体定量 2.190 [阴性(-)](COI)，乙肝e抗体定量 1.550 [阴性(-)](COI)，乙肝表面抗原定量 0.253 [阴性(-)](COI)，乙肝表面抗体定量 2 [阴性(-)](IU/L)，乙肝e抗原定量 0.095 [阴性(-)](COI)；2021-04-09 血清超敏C反应蛋白（hs-CRP)测定:超敏C反应蛋白 31.70(mg/l)↑；化验及检查提示腹腔内存在感染，十二指肠或胃穿孔包裹可能。入院后给与抗感染、抑酸、护胃、对症支持等治疗。后复查增强CT：2021-04-12 腹盆CT平扫+增强（含体层成像及三维重建）,胃窦部及十二直肠球部肠壁水肿，局部近浆膜层斑点状积气影；周围脂肪间隙模糊；结肠肝区肠壁稍厚。胆汁淤积；盆腔积液；请结合临床。保守治疗后患儿病情好转，近期复查：2021-04-19 血清超敏C反应蛋白（hs-CRP)测定:超敏C反应蛋白 1.91(mg/l)；2021-04-19 血清淀粉样蛋白A(SAA)测定:血清淀粉样蛋白A 5.50(mg/L)；2021-04-16 腹盆CT平扫（含体层成像及三维重建）,胃窦部及十二直肠球部局部近浆膜层斑点状积气影，较2021.04.11老片稍吸收；
 结肠肝区肠壁稍厚；胆汁淤积；盆腔积液；请结合临床。2021-04-14 血清幽门螺旋杆菌(HP)芯片检测:尿素酶 阳性(+)↑，细胞毒素相关蛋白 阳性(+)↑，空泡毒素相关蛋白 阳性(+)↑；患儿HP感染，请消化内科会诊建议三联疗法（甲硝唑、阿莫西林、奥美拉唑），今病情平稳家长要求出院，告知风险及注意事项，签字予以出院。</t>
         </is>
       </c>
-      <c r="AA39" s="6" t="inlineStr">
+      <c r="AA39" s="5" t="inlineStr">
         <is>
           <t>?3消化性溃疡</t>
         </is>
       </c>
-      <c r="AB39" s="6" t="inlineStr"/>
-      <c r="AC39" s="6" t="inlineStr"/>
-      <c r="AD39" s="6" t="inlineStr"/>
-      <c r="AE39" s="6" t="inlineStr"/>
-      <c r="AF39" s="6" t="inlineStr"/>
-      <c r="AG39" s="6" t="inlineStr"/>
-      <c r="AH39" s="6" t="inlineStr"/>
-      <c r="AI39" s="6" t="inlineStr"/>
-      <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="6" t="inlineStr"/>
-      <c r="AL39" s="6" t="inlineStr"/>
-      <c r="AM39" s="6" t="inlineStr"/>
-      <c r="AN39" s="6" t="inlineStr"/>
-      <c r="AO39" s="6" t="inlineStr"/>
-      <c r="AP39" s="6" t="inlineStr"/>
-      <c r="AQ39" s="6" t="inlineStr"/>
+      <c r="AB39" s="5" t="inlineStr"/>
+      <c r="AC39" s="5" t="inlineStr"/>
+      <c r="AD39" s="5" t="inlineStr"/>
+      <c r="AE39" s="5" t="inlineStr"/>
+      <c r="AF39" s="5" t="inlineStr"/>
+      <c r="AG39" s="5" t="inlineStr"/>
+      <c r="AH39" s="5" t="inlineStr"/>
+      <c r="AI39" s="5" t="inlineStr"/>
+      <c r="AJ39" s="5" t="inlineStr"/>
+      <c r="AK39" s="5" t="inlineStr"/>
+      <c r="AL39" s="5" t="inlineStr"/>
+      <c r="AM39" s="5" t="inlineStr"/>
+      <c r="AN39" s="5" t="inlineStr"/>
+      <c r="AO39" s="5" t="inlineStr"/>
+      <c r="AP39" s="5" t="inlineStr"/>
+      <c r="AQ39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -8092,121 +8108,121 @@
       <c r="AQ51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n">
+      <c r="A52" s="5" t="n">
         <v>4241876</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="5" t="n">
         <v>100462712</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C52" s="5" t="n">
         <v>2120133</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录+第2次住院</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G52" s="5" t="n">
         <v>5.49</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H52" s="5" t="n">
         <v>2004</v>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>4学龄前</t>
         </is>
       </c>
-      <c r="J52" s="6" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="K52" s="6" t="n">
+      <c r="K52" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="L52" s="6" t="n">
+      <c r="L52" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="M52" s="6" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>普外一病区</t>
         </is>
       </c>
-      <c r="N52" s="6" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔(术后)</t>
         </is>
       </c>
-      <c r="O52" s="6" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔</t>
         </is>
       </c>
-      <c r="P52" s="6" t="inlineStr">
+      <c r="P52" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔 | 手术后随诊检查</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr">
+      <c r="Q52" s="5" t="inlineStr"/>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="5" t="inlineStr"/>
+      <c r="T52" s="5" t="inlineStr"/>
+      <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔术后21天</t>
         </is>
       </c>
-      <c r="W52" s="6" t="inlineStr">
+      <c r="W52" s="5" t="inlineStr">
         <is>
           <t>21天前患儿因“十二指肠穿孔、结肠内异物”在我科行“腹腔镜中转剖腹探查术+鼻空肠营养管置入术+异物取出术”，术后恢复顺利，术后带空肠营养管出院，出院后无明显异常。近期无发热、腹泻、咳嗽等不适。今来我院，拟入院拔除空肠营养管，门诊以“十二指肠穿孔术后”收入院。        患儿自发病以来，精神食欲睡眠可，小便正常，大便正常。</t>
         </is>
       </c>
-      <c r="X52" s="6" t="inlineStr">
+      <c r="X52" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y52" s="6" t="inlineStr">
+      <c r="Y52" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神睡眠好，饮水无呕吐，无腹痛，无呕吐，无发热，大便正常，小便正常。查体：T:36.5℃。神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。伤口包扎好，敷料干燥。</t>
         </is>
       </c>
-      <c r="Z52" s="6" t="inlineStr">
+      <c r="Z52" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔术后21天，患者既往平时健康情况：一般，疾病史：无疾病史，外伤史：否认外伤史，过敏史：无，体温36.6℃，呼吸21次/分，规则，脉搏104次/分，规则，血压-/-mmHg，体重22.5Kg ，身长116cm，发育良好，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜巩膜无黄染，瞳孔等圆等大3mm，瞳孔对光反射正常，唇红润，扁桃体双侧无肿大，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率104次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，全腹柔软，无压痛，无反跳痛，肝脏肋下未触及，胆囊Murphy征阴性，脾脏肋下未触及，腹部包块见专科体检，移动性浊音呈阴性，肠鸣音正常，无肾区叩痛，四肢正常，脊柱生理弯曲存在，无病理性畸形，病理反射无，Babinski征阴性。  腹部平坦，左侧腹可见一手术疤痕，长约10cm，无明显疤痕增生，左侧腹可见一空肠营养管，营养管周围皮肤无明显红肿渗液。全腹无压痛反跳痛，未扪及包块,肠鸣音基本正常。 我院2021-11-03新冠病毒核酸及血液分析未见明显异常。  入院后完善相关检查，于2021-11-05拔空肠营养管，行抗感染、补液对症等治疗。2021-11-08 上消化道碘水造影,十二指肠水平段扩张，10分钟后复查，对比剂通过可。饮水无呕吐，今病情平稳，家长要求出院，告知风险及注意事项，签字予以出院。</t>
         </is>
       </c>
-      <c r="AA52" s="6" t="inlineStr">
+      <c r="AA52" s="5" t="inlineStr">
         <is>
           <t>?5医源性</t>
         </is>
       </c>
-      <c r="AB52" s="6" t="inlineStr"/>
-      <c r="AC52" s="6" t="inlineStr"/>
-      <c r="AD52" s="6" t="inlineStr"/>
-      <c r="AE52" s="6" t="inlineStr"/>
-      <c r="AF52" s="6" t="inlineStr"/>
-      <c r="AG52" s="6" t="inlineStr"/>
-      <c r="AH52" s="6" t="inlineStr"/>
-      <c r="AI52" s="6" t="inlineStr"/>
-      <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="6" t="inlineStr"/>
-      <c r="AL52" s="6" t="inlineStr"/>
-      <c r="AM52" s="6" t="inlineStr"/>
-      <c r="AN52" s="6" t="inlineStr"/>
-      <c r="AO52" s="6" t="inlineStr"/>
-      <c r="AP52" s="6" t="inlineStr"/>
-      <c r="AQ52" s="6" t="inlineStr"/>
+      <c r="AB52" s="5" t="inlineStr"/>
+      <c r="AC52" s="5" t="inlineStr"/>
+      <c r="AD52" s="5" t="inlineStr"/>
+      <c r="AE52" s="5" t="inlineStr"/>
+      <c r="AF52" s="5" t="inlineStr"/>
+      <c r="AG52" s="5" t="inlineStr"/>
+      <c r="AH52" s="5" t="inlineStr"/>
+      <c r="AI52" s="5" t="inlineStr"/>
+      <c r="AJ52" s="5" t="inlineStr"/>
+      <c r="AK52" s="5" t="inlineStr"/>
+      <c r="AL52" s="5" t="inlineStr"/>
+      <c r="AM52" s="5" t="inlineStr"/>
+      <c r="AN52" s="5" t="inlineStr"/>
+      <c r="AO52" s="5" t="inlineStr"/>
+      <c r="AP52" s="5" t="inlineStr"/>
+      <c r="AQ52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8480,128 +8496,128 @@
       <c r="AQ54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n">
+      <c r="A55" s="5" t="n">
         <v>8322006</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="5" t="n">
         <v>101277097</v>
       </c>
-      <c r="C55" s="6" t="n">
+      <c r="C55" s="5" t="n">
         <v>2159811</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>女性</t>
         </is>
       </c>
-      <c r="G55" s="6" t="n">
+      <c r="G55" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="H55" s="6" t="n">
+      <c r="H55" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>1新生儿</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="K55" s="6" t="n">
+      <c r="K55" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="L55" s="6" t="n">
+      <c r="L55" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M55" s="6" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>新生儿外科病区</t>
         </is>
       </c>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>消化道穿孔</t>
         </is>
       </c>
-      <c r="O55" s="6" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>新生儿胃穿孔</t>
         </is>
       </c>
-      <c r="P55" s="6" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>低出生体重儿(1500-2499g) | 新生儿胃穿孔 | 新生儿腹膜炎，其他的 | 早产儿(孕期等于或大于32整周,但小于37整周)</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr"/>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr">
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr"/>
+      <c r="T55" s="5" t="inlineStr"/>
+      <c r="U55" s="5" t="inlineStr">
         <is>
           <t>胃插管减压</t>
         </is>
       </c>
-      <c r="V55" s="6" t="inlineStr">
+      <c r="V55" s="5" t="inlineStr">
         <is>
           <t>腹胀3小时，腹平片发现消化道穿孔2小时</t>
         </is>
       </c>
-      <c r="W55" s="6" t="inlineStr">
+      <c r="W55" s="5" t="inlineStr">
         <is>
           <t>患儿G3P2，孕33周，剖宫产，单胎，出生时体重1700g，2022-4-14 18:33出生后患儿即因“早产儿、低出生体重儿”于武汉市一医院新生儿科住院，3小时患儿无明显诱因出现腹胀，不伴呕吐、腹泻、便血、胎便排出延迟，2022-04-17 05:21 急诊行腹部X片检查提示：肝周及腹腔边缘区域见片状气体样密度影，中腹部区域见肠气影，即转诊来我院，遂以“1.消化道穿孔(？) 2.早产儿(孕期等于或大于32整周,但小于37整周) 3.低出生体重儿(1500-2499g) ”收住我科。
          起病来，患儿精神反应尚可，睡眠差，禁饮食中，小便正常，大便未解。</t>
         </is>
       </c>
-      <c r="X55" s="6" t="inlineStr">
+      <c r="X55" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般
 疾病史：有疾病史，出生后因“早产儿、低体重儿”于武汉市一医院新生儿科住院治疗
 传染病史：否认传染病史</t>
         </is>
       </c>
-      <c r="Y55" s="6" t="inlineStr">
+      <c r="Y55" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿禁食水，胃肠减压中，胃肠减压引流出绿色液体，小便一般，未见大便排出。查体：体温低，精神一般，反应欠佳，早产儿貌，皮下脂肪菲薄，心音有力，呼吸音粗，未闻及明显啰音；腹部膨隆，腹胀，腹壁红肿，未见明显胃肠型，脐带新鲜，腹肌紧张，肠鸣音弱。</t>
         </is>
       </c>
-      <c r="Z55" s="6" t="inlineStr">
+      <c r="Z55" s="5" t="inlineStr">
         <is>
           <t>腹胀3小时，腹平片发现消化道穿孔2小时，患者既往平时健康情况：一般，疾病史：有疾病史，出生后因“早产儿、低体重儿”于武汉市一医院新生儿科住院治疗，外伤史：否认外伤史，过敏史：无，体温36.5℃，呼吸40次/分，规则，脉搏138次/分，规则，血压-/-mmHg，体重1.2Kg ，身长40cm，发育不良，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门未闭合  斜径：（1.8x2.0）cm，眼睑正常，巩膜无黄染，瞳孔等圆等大2 mm，瞳孔对光反射正常，唇红润，扁桃体双侧无肿大，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率138次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形膨隆，全腹腹肌紧张，全腹压痛，有，全腹反跳痛，肝脏肋下未触及，胆囊Murphy征查体不配合，脾脏肋下未触及，未触及腹部包块，移动性浊音呈阴性，肠鸣音正常，肾区扣痛不能配合，四肢正常，脊柱生理弯曲存在，无明显病理性畸形，Babinski征查体不合作。精神反应欠佳，皮下脂肪菲薄，腹部膨隆，腹壁可见静脉，未见明显胃肠型，肠鸣音弱，全腹腹肌紧张，压之患儿哭闹加剧；肛门稍狭窄，扩张后小指可顺利进入，肛内未及明显裹手感，未及骶前包块，退指后见少许黄绿色胎便排出，未见血染。2022-04-17转诊交接单一张（腹平片：气腹）2022-04-16患儿父亲新型冠状病毒肺炎核酸阴性。入院后完善相关检查，2022-04-17 腹部立位(正侧位)X光片~胸部DR拍片(正侧位),新生儿肺炎，两肺透亮度减低，建议追踪复查；消化道穿孔。2022-04-17 心电图检查(十二通道常规)+QT离散度,窦性心律;正常心电图;QT离散度：１５ms（参考范围0-70ms）。建议行手术治疗，现家属要求拒绝手术，放弃治疗，要求出院，告知相关风险及不良后果，家属知晓，给予办理。</t>
         </is>
       </c>
-      <c r="AA55" s="6" t="inlineStr">
+      <c r="AA55" s="5" t="inlineStr">
         <is>
           <t>?6其他/待读</t>
         </is>
       </c>
-      <c r="AB55" s="6" t="inlineStr"/>
-      <c r="AC55" s="6" t="inlineStr"/>
-      <c r="AD55" s="6" t="inlineStr"/>
-      <c r="AE55" s="6" t="inlineStr"/>
-      <c r="AF55" s="6" t="inlineStr"/>
-      <c r="AG55" s="6" t="inlineStr"/>
-      <c r="AH55" s="6" t="inlineStr"/>
-      <c r="AI55" s="6" t="inlineStr"/>
-      <c r="AJ55" s="6" t="inlineStr"/>
-      <c r="AK55" s="6" t="inlineStr"/>
-      <c r="AL55" s="6" t="inlineStr"/>
-      <c r="AM55" s="6" t="inlineStr"/>
-      <c r="AN55" s="6" t="inlineStr"/>
-      <c r="AO55" s="6" t="inlineStr"/>
-      <c r="AP55" s="6" t="inlineStr"/>
-      <c r="AQ55" s="6" t="inlineStr"/>
+      <c r="AB55" s="5" t="inlineStr"/>
+      <c r="AC55" s="5" t="inlineStr"/>
+      <c r="AD55" s="5" t="inlineStr"/>
+      <c r="AE55" s="5" t="inlineStr"/>
+      <c r="AF55" s="5" t="inlineStr"/>
+      <c r="AG55" s="5" t="inlineStr"/>
+      <c r="AH55" s="5" t="inlineStr"/>
+      <c r="AI55" s="5" t="inlineStr"/>
+      <c r="AJ55" s="5" t="inlineStr"/>
+      <c r="AK55" s="5" t="inlineStr"/>
+      <c r="AL55" s="5" t="inlineStr"/>
+      <c r="AM55" s="5" t="inlineStr"/>
+      <c r="AN55" s="5" t="inlineStr"/>
+      <c r="AO55" s="5" t="inlineStr"/>
+      <c r="AP55" s="5" t="inlineStr"/>
+      <c r="AQ55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -10153,121 +10169,121 @@
       <c r="AQ66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n">
+      <c r="A67" s="5" t="n">
         <v>10690905</v>
       </c>
-      <c r="B67" s="6" t="n">
+      <c r="B67" s="5" t="n">
         <v>101397996</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="5" t="n">
         <v>2226623</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="G67" s="5" t="n">
         <v>12.91</v>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H67" s="5" t="n">
         <v>4717</v>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>2023-01-21</t>
         </is>
       </c>
-      <c r="K67" s="6" t="n">
+      <c r="K67" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="L67" s="6" t="n">
+      <c r="L67" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="M67" s="6" t="inlineStr">
+      <c r="M67" s="5" t="inlineStr">
         <is>
           <t>重症医学科病区</t>
         </is>
       </c>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t>十二指肠损伤</t>
         </is>
       </c>
-      <c r="O67" s="6" t="inlineStr">
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>胰腺损伤</t>
         </is>
       </c>
-      <c r="P67" s="6" t="inlineStr">
+      <c r="P67" s="5" t="inlineStr">
         <is>
           <t>十二指肠损伤 | 升结肠损伤 | 胰腺损伤 | 胃损伤 | 横结肠损伤</t>
         </is>
       </c>
-      <c r="Q67" s="6" t="inlineStr"/>
-      <c r="R67" s="6" t="inlineStr"/>
-      <c r="S67" s="6" t="inlineStr"/>
-      <c r="T67" s="6" t="inlineStr"/>
-      <c r="U67" s="6" t="inlineStr"/>
-      <c r="V67" s="6" t="inlineStr">
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr"/>
+      <c r="S67" s="5" t="inlineStr"/>
+      <c r="T67" s="5" t="inlineStr"/>
+      <c r="U67" s="5" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr">
         <is>
           <t>腹部外伤后腹痛1天余</t>
         </is>
       </c>
-      <c r="W67" s="6" t="inlineStr">
+      <c r="W67" s="5" t="inlineStr">
         <is>
           <t>患儿1天前跑步时摔倒，腹部撞击石墩，伤后出现腹痛，程度较轻，无呕吐，无发热，无腹泻，当时未予特殊处理。今日患儿出现腹痛较前加重，伴呕吐胃内容物1次，家长遂就诊于当地医院，予以完善腹部CT示胃体-胃窦及邻近胰腺周围渗出，胃窦-十二指肠交界区周围少许小气泡影：考虑空腔脏器穿孔可能性大，合并胰腺损伤不除外，家长为求进一步诊治遂来我院就诊，急诊以“十二指肠损伤、胰腺损伤”收入我科。         病后精神反应尚可，食欲尚可，睡眠尚可，大小便如常。</t>
         </is>
       </c>
-      <c r="X67" s="6" t="inlineStr">
+      <c r="X67" s="5" t="inlineStr">
         <is>
           <t>平时健康情况:一般          疾病史:无疾病史         传染病史：否认传染病史</t>
         </is>
       </c>
-      <c r="Y67" s="6" t="inlineStr">
+      <c r="Y67" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神食欲睡眠好，无腹痛，无呕吐，无发热，大便正常，小便正常。查体：神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。伤口包扎好，敷料干燥。</t>
         </is>
       </c>
-      <c r="Z67" s="6" t="inlineStr">
+      <c r="Z67" s="5" t="inlineStr">
         <is>
           <t>腹部外伤后腹痛1天余，患者既往平时健康情况：一般，疾病史：无疾病史，外伤史：否认外伤史，过敏史：无，体温36.5℃，呼吸27次/分，规则，脉搏95次/分，血压112/67mmHg，体重34Kg ，身长142cm，发育良好，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜无黄染，瞳孔等圆等大2.5mm，瞳孔对光反射正常，唇红润，咽无充血，扁桃体双侧无肿大，呼吸音正常，未闻及肺部啰音，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，肝脏肋下未触及，脾脏肋下未触及，未触及腹部包块，肠鸣音稍减弱，约2-3次/分，脊柱生理弯曲存在，无病理性畸形，Kerning征阴性，Brudzinski征阴性。  神志清楚，双肺未闻及啰音，腹部平软，上腹部有压痛，无反跳痛，肝脾肋下未触及 2023-01-21 全腹部CT：1.胃体-胃窦及邻近胰腺周围渗出，胃窦-十二指肠交界区周围少许小气泡影：考虑空腔脏器穿孔可能性大，合并胰腺损伤不除外，请结合临床分析及治疗后复查。2.盆腔少量积液。  入院后完善相关检查，于重症医学科，2023-01-22 腹盆CT平扫（含体层成像及三维重建）,胃、十二指肠、横结肠及升结肠壁肿胀、增厚，周围渗出。胰腺损伤。肠系膜肿胀。盆腔少许积液；保守治疗后转入我科继续治疗，今复查：2023-01-29 腹盆CT平扫+增强（含体层成像及三维重建）,胃窦部、结肠肿胀。胰腺损伤。上述异常表现较前（2023-1-22）明显改善。今病情平稳，家长要求出院，告知风险及注意事项，签字予以出院。</t>
         </is>
       </c>
-      <c r="AA67" s="6" t="inlineStr">
+      <c r="AA67" s="5" t="inlineStr">
         <is>
           <t>?4创伤</t>
         </is>
       </c>
-      <c r="AB67" s="6" t="inlineStr"/>
-      <c r="AC67" s="6" t="inlineStr"/>
-      <c r="AD67" s="6" t="inlineStr"/>
-      <c r="AE67" s="6" t="inlineStr"/>
-      <c r="AF67" s="6" t="inlineStr"/>
-      <c r="AG67" s="6" t="inlineStr"/>
-      <c r="AH67" s="6" t="inlineStr"/>
-      <c r="AI67" s="6" t="inlineStr"/>
-      <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="6" t="inlineStr"/>
-      <c r="AL67" s="6" t="inlineStr"/>
-      <c r="AM67" s="6" t="inlineStr"/>
-      <c r="AN67" s="6" t="inlineStr"/>
-      <c r="AO67" s="6" t="inlineStr"/>
-      <c r="AP67" s="6" t="inlineStr"/>
-      <c r="AQ67" s="6" t="inlineStr"/>
+      <c r="AB67" s="5" t="inlineStr"/>
+      <c r="AC67" s="5" t="inlineStr"/>
+      <c r="AD67" s="5" t="inlineStr"/>
+      <c r="AE67" s="5" t="inlineStr"/>
+      <c r="AF67" s="5" t="inlineStr"/>
+      <c r="AG67" s="5" t="inlineStr"/>
+      <c r="AH67" s="5" t="inlineStr"/>
+      <c r="AI67" s="5" t="inlineStr"/>
+      <c r="AJ67" s="5" t="inlineStr"/>
+      <c r="AK67" s="5" t="inlineStr"/>
+      <c r="AL67" s="5" t="inlineStr"/>
+      <c r="AM67" s="5" t="inlineStr"/>
+      <c r="AN67" s="5" t="inlineStr"/>
+      <c r="AO67" s="5" t="inlineStr"/>
+      <c r="AP67" s="5" t="inlineStr"/>
+      <c r="AQ67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -11153,148 +11169,148 @@
       <c r="AQ73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="n">
+      <c r="A74" s="5" t="n">
         <v>8693016</v>
       </c>
-      <c r="B74" s="6" t="n">
+      <c r="B74" s="5" t="n">
         <v>101429169</v>
       </c>
-      <c r="C74" s="6" t="n">
+      <c r="C74" s="5" t="n">
         <v>2259289</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>⚠第4次住院</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>女性</t>
         </is>
       </c>
-      <c r="G74" s="6" t="n">
+      <c r="G74" s="5" t="n">
         <v>2.07</v>
       </c>
-      <c r="H74" s="6" t="n">
+      <c r="H74" s="5" t="n">
         <v>757</v>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>3幼儿</t>
         </is>
       </c>
-      <c r="J74" s="6" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="K74" s="6" t="n">
+      <c r="K74" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="L74" s="6" t="n">
+      <c r="L74" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="M74" s="6" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>普外一病区</t>
         </is>
       </c>
-      <c r="N74" s="6" t="inlineStr">
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>消化道内异物</t>
         </is>
       </c>
-      <c r="O74" s="6" t="inlineStr">
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P74" s="6" t="inlineStr">
+      <c r="P74" s="5" t="inlineStr">
         <is>
           <t>肠系膜损伤 | 小肠穿孔 | 胃穿孔 | 小肠内异物 | 局限性腹膜炎 | 胃内异物</t>
         </is>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
+      <c r="Q74" s="5" t="inlineStr">
         <is>
           <t>胃穿孔(1处),小肠穿孔(3处),(结肠)肠系膜损伤(2处穿孔),胃内异物(磁珠1枚),小肠内异物(磁珠12枚),局限性腹膜炎</t>
         </is>
       </c>
-      <c r="R74" s="6" t="inlineStr">
+      <c r="R74" s="5" t="inlineStr">
         <is>
           <t>胃破裂修补术+小肠破裂修补术+胃和小肠管腔内异物的不切开去除+经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="S74" s="6" t="inlineStr">
+      <c r="S74" s="5" t="inlineStr">
         <is>
           <t>1、麻醉成功后取仰卧位，常规消毒，铺巾，上导尿管顺利。
 2、取右腹脐上横切口，长约6cm，逐层进腹。进腹探查见腹膜轻度充血，腹腔渗液清亮，量少，部分小肠肠管扩张，距屈氏韧带50cm处肠管，110cm处肠管，120cm处肠管有破裂，并形成索带压迫回肠，其内可探及数枚磁珠，磁珠相互吸引，分离索带后顺利取出12枚磁珠，继续探查见肠系膜有2处穿孔，胃有1处破裂，顺利取出1枚磁珠，5-0可吸收线连续浆肌层缝合上述穿孔部位，并间断缝合包埋，扩张肠管减压后检查腹腔无明显出血，蛇毒血凝酶冲洗腹腔，吸尽积液后医用透明质酸钠留置腹腔防粘连，右下腹留置腹腔引流管一根。再次检查腹腔无明显出血及积液，2-0可吸收线连续缝合腹膜，逐层缝合皮下组织，5-0可吸收线皮内缝合切口，医用组织胶粘合，外用手术止血纱包扎。
 3、术毕安返病房。术中出血5ml，尿量40ml。</t>
         </is>
       </c>
-      <c r="T74" s="6" t="inlineStr">
+      <c r="T74" s="5" t="inlineStr">
         <is>
           <t>2023-05-11 00:00</t>
         </is>
       </c>
-      <c r="U74" s="6" t="inlineStr">
+      <c r="U74" s="5" t="inlineStr">
         <is>
           <t>小肠破裂修补术 | 经腹盆腔穿刺引流术 | 胃和小肠管腔内异物的不切开去除 | 胃破裂修补术</t>
         </is>
       </c>
-      <c r="V74" s="6" t="inlineStr">
+      <c r="V74" s="5" t="inlineStr">
         <is>
           <t>误食异物4天</t>
         </is>
       </c>
-      <c r="W74" s="6" t="inlineStr">
+      <c r="W74" s="5" t="inlineStr">
         <is>
           <t>4天前患儿玩耍时不慎吞食异物，异物为磁力珠，无发热、无恶心、无呕吐、伴腹痛。未予特殊治疗，无好转。今来我院急诊就诊，2023-05-11亚心医院平片提示消化道内异物，以"消化道异物"收入院。        患儿自发病以来，精神食欲睡眠一般，小便正常，大便正常。</t>
         </is>
       </c>
-      <c r="X74" s="6" t="inlineStr">
+      <c r="X74" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y74" s="6" t="inlineStr">
+      <c r="Y74" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神食欲睡眠好，无腹痛，无呕吐，无发热，大便正常，小便正常。查体：神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。伤口包扎好，敷料干燥。</t>
         </is>
       </c>
-      <c r="Z74" s="6" t="inlineStr">
+      <c r="Z74" s="5" t="inlineStr">
         <is>
           <t>误食异物4天，患者既往平时健康情况：一般，疾病史：无疾病史，外伤史：否认外伤史，过敏史：无，体温36.6℃，呼吸21次/分，规则，脉搏100次/分，规则，血压107/70mmHg，体重11Kg ，身长93cm，发育良好，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜巩膜无黄染，瞳孔等圆等大4mm，瞳孔对光反射正常，唇红润，扁桃体双侧无肿大，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率100次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，全腹柔软，无压痛，无反跳痛，肝脏肋下未触及，胆囊Murphy征阴性，脾脏肋下未触及，未触及腹部包块，移动性浊音呈阴性，肠鸣音正常，无肾区叩痛，四肢正常，，脊柱生理弯曲存在，无病理性畸形，病理反射无，Babinski征阴性。  腹部平坦，未见胃肠型；触：右侧腹部肌紧，右侧腹压痛阳性，反跳痛阴性，未扪及包块；叩：移动性浊音阴性；听：肠鸣音正常，4次/分； 外院2023-05-11腹部立位片：腹部不透光异物影。  
     入院后完善相关检查，2023-05-11  血型测定(正反定型):Rh(D)血型 阳性，ABO血型 A型；2023-05-12  血清乙肝全套(五项）检测:乙肝病毒表面抗体定量 284(IU/L)↑；2023-05-16  血液分析五分类（血常规)（静脉血）:白细胞计数 8.00(10^9/L)；2023-05-16  血清降钙素原(PCT)定量测定:降钙素原 0.190(ng/ml)↑；2023-05-16  血清超敏C反应蛋白（hs-CRP)测定:超敏C反应蛋白 2.93(mg/L)；于2023-05-11 全麻下胃破裂修补术+小肠破裂修补术+胃和小肠管腔内异物的不切开去除+经腹盆腔穿刺引流术，行抗感染、止血、补液对症等治疗，今病情稳定，临床治愈，征得家长同意，予以出院。</t>
         </is>
       </c>
-      <c r="AA74" s="6" t="inlineStr">
+      <c r="AA74" s="5" t="inlineStr">
         <is>
           <t>?1异物相关</t>
         </is>
       </c>
-      <c r="AB74" s="6" t="inlineStr">
+      <c r="AB74" s="5" t="inlineStr">
         <is>
           <t>磁珠</t>
         </is>
       </c>
-      <c r="AC74" s="6" t="inlineStr"/>
-      <c r="AD74" s="6" t="inlineStr"/>
-      <c r="AE74" s="6" t="inlineStr"/>
-      <c r="AF74" s="6" t="inlineStr"/>
-      <c r="AG74" s="6" t="inlineStr"/>
-      <c r="AH74" s="6" t="inlineStr"/>
-      <c r="AI74" s="6" t="inlineStr"/>
-      <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="6" t="inlineStr"/>
-      <c r="AL74" s="6" t="inlineStr"/>
-      <c r="AM74" s="6" t="inlineStr"/>
-      <c r="AN74" s="6" t="inlineStr"/>
-      <c r="AO74" s="6" t="inlineStr"/>
-      <c r="AP74" s="6" t="inlineStr"/>
-      <c r="AQ74" s="6" t="inlineStr"/>
+      <c r="AC74" s="5" t="inlineStr"/>
+      <c r="AD74" s="5" t="inlineStr"/>
+      <c r="AE74" s="5" t="inlineStr"/>
+      <c r="AF74" s="5" t="inlineStr"/>
+      <c r="AG74" s="5" t="inlineStr"/>
+      <c r="AH74" s="5" t="inlineStr"/>
+      <c r="AI74" s="5" t="inlineStr"/>
+      <c r="AJ74" s="5" t="inlineStr"/>
+      <c r="AK74" s="5" t="inlineStr"/>
+      <c r="AL74" s="5" t="inlineStr"/>
+      <c r="AM74" s="5" t="inlineStr"/>
+      <c r="AN74" s="5" t="inlineStr"/>
+      <c r="AO74" s="5" t="inlineStr"/>
+      <c r="AP74" s="5" t="inlineStr"/>
+      <c r="AQ74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11590,126 +11606,126 @@
       <c r="AQ76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n">
+      <c r="A77" s="5" t="n">
         <v>17560600</v>
       </c>
-      <c r="B77" s="6" t="n">
+      <c r="B77" s="5" t="n">
         <v>101516546</v>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="5" t="n">
         <v>2332079</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录+第2次住院</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G77" s="6" t="n">
+      <c r="G77" s="5" t="n">
         <v>0.14</v>
       </c>
-      <c r="H77" s="6" t="n">
+      <c r="H77" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>2婴儿</t>
         </is>
       </c>
-      <c r="J77" s="6" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>2023-12-02</t>
         </is>
       </c>
-      <c r="K77" s="6" t="n">
+      <c r="K77" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="L77" s="6" t="n">
+      <c r="L77" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M77" s="6" t="inlineStr">
+      <c r="M77" s="5" t="inlineStr">
         <is>
           <t>新生儿外科病区</t>
         </is>
       </c>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="N77" s="5" t="inlineStr">
         <is>
           <t>新生儿胃穿孔(术后)</t>
         </is>
       </c>
-      <c r="O77" s="6" t="inlineStr">
+      <c r="O77" s="5" t="inlineStr">
         <is>
           <t>呕吐</t>
         </is>
       </c>
-      <c r="P77" s="6" t="inlineStr">
+      <c r="P77" s="5" t="inlineStr">
         <is>
           <t>呕吐 | 胃术后</t>
         </is>
       </c>
-      <c r="Q77" s="6" t="inlineStr"/>
-      <c r="R77" s="6" t="inlineStr"/>
-      <c r="S77" s="6" t="inlineStr"/>
-      <c r="T77" s="6" t="inlineStr"/>
-      <c r="U77" s="6" t="inlineStr"/>
-      <c r="V77" s="6" t="inlineStr">
+      <c r="Q77" s="5" t="inlineStr"/>
+      <c r="R77" s="5" t="inlineStr"/>
+      <c r="S77" s="5" t="inlineStr"/>
+      <c r="T77" s="5" t="inlineStr"/>
+      <c r="U77" s="5" t="inlineStr"/>
+      <c r="V77" s="5" t="inlineStr">
         <is>
           <t>间断呕吐伴哭闹不安半天。</t>
         </is>
       </c>
-      <c r="W77" s="6" t="inlineStr">
+      <c r="W77" s="5" t="inlineStr">
         <is>
           <t>患儿G5P3，孕35周+6天，剖宫产，单胎，出生时体重3300g，半天前患儿无明显诱因出院呕吐，呕吐物为白色奶汁，共呕吐4次，均为进奶后呕吐，伴哭闹不安，为进一步诊治，遂急诊来我院，急诊查体后以“胃修补术后、肠旋转不良术后”收住我科。
     自出生后患儿精神、睡眠、反应可，大、小便正常。</t>
         </is>
       </c>
-      <c r="X77" s="6" t="inlineStr">
+      <c r="X77" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般
 疾病史：有疾病史，2023-10-17至2023-11-29因“先天性胃壁肌层缺损,新生儿胃穿孔,先天性肠旋转不良,新生儿腹膜炎，其他的,腹腔积液,早产儿(孕期等于或大于32整周,但小于37整周),新生儿肺炎,(左侧)气胸,(双侧)先天性鞘膜积液,胃潴留,先天性喉喘鸣,贫血”于我科住院治疗
 传染病史：否认传染病史</t>
         </is>
       </c>
-      <c r="Y77" s="6" t="inlineStr">
+      <c r="Y77" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神食欲睡眠好，无发热，大便正常，小便正常。体检：神志清楚，反应可，心音有力，心律齐，呼吸平稳，双侧呼吸音清，腹部外形平坦，腹肌软，肠鸣音正常。</t>
         </is>
       </c>
-      <c r="Z77" s="6" t="inlineStr">
+      <c r="Z77" s="5" t="inlineStr">
         <is>
           <t>间断呕吐伴哭闹不安半天。有疾病史，2023-10-17至2023-11-29因“先天性胃壁肌层缺损,新生儿胃穿孔,先天性肠旋转不良,新生儿腹膜炎，其他的,腹腔积液,早产儿(孕期等于或大于32整周,但小于37整周),新生儿肺炎,(左侧)气胸,(双侧)先天性鞘膜积液,胃潴留,先天性喉喘鸣,贫血”于我科住院治疗，外伤史：否认外伤史，过敏史：无，体温36.6℃，呼吸33次/分，规则，脉搏135次/分，体重4.0Kg ，身长57.0cm，发育良好，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门未闭合  斜径：（1.8x2.0）cm，眼睑正常，巩膜无黄染，瞳孔等圆等大2 mm，瞳孔对光反射正常，唇红润，扁桃体双侧无肿大，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率135次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，全腹柔软，无压痛，无反跳痛，肝脏肋下未触及，胆囊Murphy征查体不配合，脾脏肋下未触及，未触及腹部包块，移动性浊音呈阴性，肠鸣音正常，无肾区扣痛，四肢正常，脊柱生理弯曲存在，无明显病理性畸形，Babinski征查体不合作。腹部平软，无胃肠型，无腹壁静脉曲张，中上腹部可见既往手术瘢痕；全腹压痛阴性，反跳痛阴性，未扪及包块；移动性浊音阴性；肠鸣音正常，3次/分。 
 入院后完善相关检查，血常规、肝肾功能、电解质未见明显异常。2023-12-02 心电图检查(十二通道常规)+QT离散度,窦性心律;正常心电图;2023-12-02 胸腹正立位X光片：两肺纹理增强，腹部未见明显异常。
 入院后予头高足低位、少量多餐喂养，无频繁呕吐等不适，今病情稳定，临床治愈，征得家长同意，予以出院。</t>
         </is>
       </c>
-      <c r="AA77" s="6" t="inlineStr">
+      <c r="AA77" s="5" t="inlineStr">
         <is>
           <t>?5医源性</t>
         </is>
       </c>
-      <c r="AB77" s="6" t="inlineStr"/>
-      <c r="AC77" s="6" t="inlineStr"/>
-      <c r="AD77" s="6" t="inlineStr"/>
-      <c r="AE77" s="6" t="inlineStr"/>
-      <c r="AF77" s="6" t="inlineStr"/>
-      <c r="AG77" s="6" t="inlineStr"/>
-      <c r="AH77" s="6" t="inlineStr"/>
-      <c r="AI77" s="6" t="inlineStr"/>
-      <c r="AJ77" s="6" t="inlineStr"/>
-      <c r="AK77" s="6" t="inlineStr"/>
-      <c r="AL77" s="6" t="inlineStr"/>
-      <c r="AM77" s="6" t="inlineStr"/>
-      <c r="AN77" s="6" t="inlineStr"/>
-      <c r="AO77" s="6" t="inlineStr"/>
-      <c r="AP77" s="6" t="inlineStr"/>
-      <c r="AQ77" s="6" t="inlineStr"/>
+      <c r="AB77" s="5" t="inlineStr"/>
+      <c r="AC77" s="5" t="inlineStr"/>
+      <c r="AD77" s="5" t="inlineStr"/>
+      <c r="AE77" s="5" t="inlineStr"/>
+      <c r="AF77" s="5" t="inlineStr"/>
+      <c r="AG77" s="5" t="inlineStr"/>
+      <c r="AH77" s="5" t="inlineStr"/>
+      <c r="AI77" s="5" t="inlineStr"/>
+      <c r="AJ77" s="5" t="inlineStr"/>
+      <c r="AK77" s="5" t="inlineStr"/>
+      <c r="AL77" s="5" t="inlineStr"/>
+      <c r="AM77" s="5" t="inlineStr"/>
+      <c r="AN77" s="5" t="inlineStr"/>
+      <c r="AO77" s="5" t="inlineStr"/>
+      <c r="AP77" s="5" t="inlineStr"/>
+      <c r="AQ77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11853,81 +11869,81 @@
       <c r="AQ78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="n">
+      <c r="A79" s="5" t="n">
         <v>35650146</v>
       </c>
-      <c r="B79" s="6" t="n">
+      <c r="B79" s="5" t="n">
         <v>101589824</v>
       </c>
-      <c r="C79" s="6" t="n">
+      <c r="C79" s="5" t="n">
         <v>2405453</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>女性</t>
         </is>
       </c>
-      <c r="G79" s="6" t="n">
+      <c r="G79" s="5" t="n">
         <v>10.83</v>
       </c>
-      <c r="H79" s="6" t="n">
+      <c r="H79" s="5" t="n">
         <v>3957</v>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="K79" s="6" t="n">
+      <c r="K79" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="L79" s="6" t="n">
+      <c r="L79" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="M79" s="6" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>肝胆外科/肿瘤外科</t>
         </is>
       </c>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" s="5" t="inlineStr">
         <is>
           <t>消化道穿孔</t>
         </is>
       </c>
-      <c r="O79" s="6" t="inlineStr">
+      <c r="O79" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P79" s="6" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>胃穿孔 | 胃内异物 | 脓毒性休克 | 弥漫性腹膜炎 | 中度贫血 | 凝血功能异常 | 手术后切口脂肪液化 | 低钙血症 | 清蛋白[白蛋白]异常 | 阑尾结石</t>
         </is>
       </c>
-      <c r="Q79" s="6" t="inlineStr">
+      <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>(胃小弯)胃穿孔,胃内异物</t>
         </is>
       </c>
-      <c r="R79" s="6" t="inlineStr">
+      <c r="R79" s="5" t="inlineStr">
         <is>
           <t>胃溃疡穿孔修补术+胃切开异物取出术+经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="S79" s="6" t="inlineStr">
+      <c r="S79" s="5" t="inlineStr">
         <is>
           <t>1、麻醉成功后取仰卧位，常规消毒，铺巾，上导尿管顺利；
 2、取上腹部剑突下正中纵行切口，约10cm，逐层进腹。探查见腹腔大量黄色浑浊脓液，用吸引器吸取干净(同时送取脓液标本送检）。探查可见胃小弯处有一穿孔，大小约0.5*0.5cm，伴有胃肠内容物流出。同时可见胃明显充盈饱满，胃腔内被团块样毛发填满。
@@ -11936,54 +11952,54 @@
 5、再次检查胃部及其他肠管未见明显异常后温盐水冲洗腹腔，吸净腹腔内积液后，于左下腹、右下腹、右侧腹可取约5mm切口，分别于左结肠旁沟、盆腔及胃小弯处放置引流管。逐层关腹，间断缝合皮肤。外用敷料后加压包扎。术毕安返病房。术中出血10ml，尿量未计。术中输注去白细胞悬浮红细胞2u（血袋号：9000124111612,9000124119213），术中未见输血不良反应。</t>
         </is>
       </c>
-      <c r="T79" s="6" t="inlineStr">
+      <c r="T79" s="5" t="inlineStr">
         <is>
           <t>2024-06-28 00:00</t>
         </is>
       </c>
-      <c r="U79" s="6" t="inlineStr">
+      <c r="U79" s="5" t="inlineStr">
         <is>
           <t>经腹盆腔穿刺引流术 | 胃切开异物取出术 | 胃溃疡穿孔修补术</t>
         </is>
       </c>
-      <c r="V79" s="6" t="inlineStr">
+      <c r="V79" s="5" t="inlineStr">
         <is>
           <t>阵发性上腹腹痛5小时</t>
         </is>
       </c>
-      <c r="W79" s="6" t="inlineStr">
+      <c r="W79" s="5" t="inlineStr">
         <is>
           <t>5小时前无明显诱因患儿出现阵发性上腹腹痛，无尿频、尿急、尿痛及腰痛等不适。否认不洁饮食史，否认腹部外伤史，否认近期做过剧烈运动。患儿既往有异食癖，有食用毛发、指甲等。既往于协和区江北医院行CT检查提示消化道穿孔。今来我院门诊就诊，以“消化道穿孔”收入院。         患儿自发病以来，精神食欲睡眠欠佳，小便未排}，大便未排。</t>
         </is>
       </c>
-      <c r="X79" s="6" t="inlineStr">
+      <c r="X79" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y79" s="6" t="inlineStr"/>
-      <c r="Z79" s="6" t="inlineStr"/>
-      <c r="AA79" s="6" t="inlineStr">
+      <c r="Y79" s="5" t="inlineStr"/>
+      <c r="Z79" s="5" t="inlineStr"/>
+      <c r="AA79" s="5" t="inlineStr">
         <is>
           <t>?1异物相关</t>
         </is>
       </c>
-      <c r="AB79" s="6" t="inlineStr"/>
-      <c r="AC79" s="6" t="inlineStr"/>
-      <c r="AD79" s="6" t="inlineStr"/>
-      <c r="AE79" s="6" t="inlineStr"/>
-      <c r="AF79" s="6" t="inlineStr"/>
-      <c r="AG79" s="6" t="inlineStr"/>
-      <c r="AH79" s="6" t="inlineStr"/>
-      <c r="AI79" s="6" t="inlineStr"/>
-      <c r="AJ79" s="6" t="inlineStr"/>
-      <c r="AK79" s="6" t="inlineStr"/>
-      <c r="AL79" s="6" t="inlineStr"/>
-      <c r="AM79" s="6" t="inlineStr"/>
-      <c r="AN79" s="6" t="inlineStr"/>
-      <c r="AO79" s="6" t="inlineStr"/>
-      <c r="AP79" s="6" t="inlineStr"/>
-      <c r="AQ79" s="6" t="inlineStr"/>
+      <c r="AB79" s="5" t="inlineStr"/>
+      <c r="AC79" s="5" t="inlineStr"/>
+      <c r="AD79" s="5" t="inlineStr"/>
+      <c r="AE79" s="5" t="inlineStr"/>
+      <c r="AF79" s="5" t="inlineStr"/>
+      <c r="AG79" s="5" t="inlineStr"/>
+      <c r="AH79" s="5" t="inlineStr"/>
+      <c r="AI79" s="5" t="inlineStr"/>
+      <c r="AJ79" s="5" t="inlineStr"/>
+      <c r="AK79" s="5" t="inlineStr"/>
+      <c r="AL79" s="5" t="inlineStr"/>
+      <c r="AM79" s="5" t="inlineStr"/>
+      <c r="AN79" s="5" t="inlineStr"/>
+      <c r="AO79" s="5" t="inlineStr"/>
+      <c r="AP79" s="5" t="inlineStr"/>
+      <c r="AQ79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -12418,81 +12434,81 @@
       <c r="AQ82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="n">
+      <c r="A83" s="5" t="n">
         <v>35808566</v>
       </c>
-      <c r="B83" s="6" t="n">
+      <c r="B83" s="5" t="n">
         <v>101645494</v>
       </c>
-      <c r="C83" s="6" t="n">
+      <c r="C83" s="5" t="n">
         <v>2458931</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G83" s="6" t="n">
+      <c r="G83" s="5" t="n">
         <v>5.25</v>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H83" s="5" t="n">
         <v>1919</v>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>4学龄前</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>2024-12-14</t>
         </is>
       </c>
-      <c r="K83" s="6" t="n">
+      <c r="K83" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="L83" s="6" t="n">
+      <c r="L83" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="M83" s="6" t="inlineStr">
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>肝胆外科/肿瘤外科病区</t>
         </is>
       </c>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t>消化道内异物</t>
         </is>
       </c>
-      <c r="O83" s="6" t="inlineStr">
+      <c r="O83" s="5" t="inlineStr">
         <is>
           <t>胃内异物</t>
         </is>
       </c>
-      <c r="P83" s="6" t="inlineStr">
+      <c r="P83" s="5" t="inlineStr">
         <is>
           <t>肠系膜损伤 | 胃内异物 | 小肠内异物 | 胃穿孔 | 小肠穿孔</t>
         </is>
       </c>
-      <c r="Q83" s="6" t="inlineStr">
+      <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>胃内异物(磁力珠),小肠内异物(磁力珠),胃穿孔,小肠穿孔,肠系膜损伤</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
+      <c r="R83" s="5" t="inlineStr">
         <is>
           <t>胃切开异物取出术+小肠切开异物取出术+胃修补术+小肠破裂修补术+肠系膜修补术+腹腔镜检查</t>
         </is>
       </c>
-      <c r="S83" s="6" t="inlineStr">
+      <c r="S83" s="5" t="inlineStr">
         <is>
           <t>1、平卧位，手术区域常规消毒铺巾；
 2、脐环左右侧分别作5mm切口，常规建立ＣＯ２人工气腹，压力10mmHg，分别置入相应大小Ｔｒｏｃａ，内置腹腔镜目镜、无创血管钳或抓钳。右下腹横纹切口，置5mmＴｒｏｃａ；
@@ -12502,189 +12518,189 @@
 5、术中出血约5ml，尿量约200ml。</t>
         </is>
       </c>
-      <c r="T83" s="6" t="inlineStr">
+      <c r="T83" s="5" t="inlineStr">
         <is>
           <t>2024-12-15 00:00</t>
         </is>
       </c>
-      <c r="U83" s="6" t="inlineStr">
+      <c r="U83" s="5" t="inlineStr">
         <is>
           <t>肠系膜修补术 | 腹腔镜检查 | 胃切开异物取出术 | 小肠切开异物取出术 | 胃修补术 | 小肠破裂修补术</t>
         </is>
       </c>
-      <c r="V83" s="6" t="inlineStr">
+      <c r="V83" s="5" t="inlineStr">
         <is>
           <t>误食异物7天</t>
         </is>
       </c>
-      <c r="W83" s="6" t="inlineStr">
+      <c r="W83" s="5" t="inlineStr">
         <is>
           <t>7天前患儿玩耍时不慎吞食异物一枚，异物可能为串珠，无发热、无恶心、无呕吐、无腹痛。2024-12-07 胸肋骨CT平扫（含体层成像及三维重建）,胸骨下段凹陷，Haller指数约2.85，请结合临床。胃内高密度影，异物多考虑。未予特殊治疗，无好转。2024-12-14 崇阳县天城镇卫生院腹部x线提示：考虑腹部异物，复查位置基本同前（2024.12.08），今来我院急诊就诊，以"消化道异物"收入院。        患儿自发病以来，精神食欲睡眠一般，小便正常，大便正常。</t>
         </is>
       </c>
-      <c r="X83" s="6" t="inlineStr">
+      <c r="X83" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y83" s="6" t="inlineStr"/>
-      <c r="Z83" s="6" t="inlineStr"/>
-      <c r="AA83" s="6" t="inlineStr">
+      <c r="Y83" s="5" t="inlineStr"/>
+      <c r="Z83" s="5" t="inlineStr"/>
+      <c r="AA83" s="5" t="inlineStr">
         <is>
           <t>?1异物相关</t>
         </is>
       </c>
-      <c r="AB83" s="6" t="inlineStr">
+      <c r="AB83" s="5" t="inlineStr">
         <is>
           <t>磁力珠</t>
         </is>
       </c>
-      <c r="AC83" s="6" t="inlineStr"/>
-      <c r="AD83" s="6" t="inlineStr"/>
-      <c r="AE83" s="6" t="inlineStr"/>
-      <c r="AF83" s="6" t="inlineStr"/>
-      <c r="AG83" s="6" t="inlineStr"/>
-      <c r="AH83" s="6" t="inlineStr"/>
-      <c r="AI83" s="6" t="inlineStr"/>
-      <c r="AJ83" s="6" t="inlineStr"/>
-      <c r="AK83" s="6" t="inlineStr"/>
-      <c r="AL83" s="6" t="inlineStr"/>
-      <c r="AM83" s="6" t="inlineStr"/>
-      <c r="AN83" s="6" t="inlineStr"/>
-      <c r="AO83" s="6" t="inlineStr"/>
-      <c r="AP83" s="6" t="inlineStr"/>
-      <c r="AQ83" s="6" t="inlineStr"/>
+      <c r="AC83" s="5" t="inlineStr"/>
+      <c r="AD83" s="5" t="inlineStr"/>
+      <c r="AE83" s="5" t="inlineStr"/>
+      <c r="AF83" s="5" t="inlineStr"/>
+      <c r="AG83" s="5" t="inlineStr"/>
+      <c r="AH83" s="5" t="inlineStr"/>
+      <c r="AI83" s="5" t="inlineStr"/>
+      <c r="AJ83" s="5" t="inlineStr"/>
+      <c r="AK83" s="5" t="inlineStr"/>
+      <c r="AL83" s="5" t="inlineStr"/>
+      <c r="AM83" s="5" t="inlineStr"/>
+      <c r="AN83" s="5" t="inlineStr"/>
+      <c r="AO83" s="5" t="inlineStr"/>
+      <c r="AP83" s="5" t="inlineStr"/>
+      <c r="AQ83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n">
+      <c r="A84" s="5" t="n">
         <v>35826208</v>
       </c>
-      <c r="B84" s="6" t="n">
+      <c r="B84" s="5" t="n">
         <v>101649227</v>
       </c>
-      <c r="C84" s="6" t="n">
+      <c r="C84" s="5" t="n">
         <v>2462824</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>女性</t>
         </is>
       </c>
-      <c r="G84" s="6" t="n">
+      <c r="G84" s="5" t="n">
         <v>13.51</v>
       </c>
-      <c r="H84" s="6" t="n">
+      <c r="H84" s="5" t="n">
         <v>4936</v>
       </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J84" s="6" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>2024-12-26</t>
         </is>
       </c>
-      <c r="K84" s="6" t="n">
+      <c r="K84" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="L84" s="6" t="n">
+      <c r="L84" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="M84" s="6" t="inlineStr">
+      <c r="M84" s="5" t="inlineStr">
         <is>
           <t>肝胆外科/肿瘤外科病区</t>
         </is>
       </c>
-      <c r="N84" s="6" t="inlineStr">
+      <c r="N84" s="5" t="inlineStr">
         <is>
           <t>腹膜炎</t>
         </is>
       </c>
-      <c r="O84" s="6" t="inlineStr">
+      <c r="O84" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P84" s="6" t="inlineStr">
+      <c r="P84" s="5" t="inlineStr">
         <is>
           <t>胃穿孔 | 弥漫性腹膜炎 | 肠粘连 | 呼吸道感染 | 甲型H1N1流行性感冒</t>
         </is>
       </c>
-      <c r="Q84" s="6" t="inlineStr">
+      <c r="Q84" s="5" t="inlineStr">
         <is>
           <t>胃穿孔,弥漫性腹膜炎,肠粘连</t>
         </is>
       </c>
-      <c r="R84" s="6" t="inlineStr">
+      <c r="R84" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃修补术+腹腔镜下肠粘连松解术+经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="S84" s="6" t="inlineStr">
+      <c r="S84" s="5" t="inlineStr">
         <is>
           <t>1.取仰卧位，麻醉满意后，留置导尿管，常规消毒铺巾。
 2.脐环上侧、剑突下6cm、左锁骨中线脐平行处分别作5.5mm、5.5mm、5.5mm切口，常规建立CO2人工气腹，压力10mmHg，分别置入相应大小Trocar，探查见腹腔内大量黄色浑浊渗液及脓苔附着，取部分液体送细菌培养及药敏试验，小肠全段及结肠未见坏死穿孔，肠壁水肿、粘连，胃窦前壁可见约2x2cm大小破裂口，粘膜水肿出血，在剑突下左侧经腹壁穿入2-0医用可吸收性缝合线，缝挂近肝实质处的肝圆韧带，然后把针从肝镰状韧带的右侧穿出腹壁，上拉缝线，充分暴露手术视野，于2-0丝线连续缝合修补穿孔的胃壁，胃壁浆膜层再缝合包埋一次，检查修补处无漏气漏液，血运良好，检查手术野无活动性出血，温盐水反复冲洗腹腔，吸尽腹腔积液后。左下腹置腹腔引流管一根于肝下最低处。解除气腹，拔出各个Trocar，对合伤口皮肤，5-0可吸收线缝合5.0mm切口皮下，医用组织胶粘合，外用手术止血纱（速绫）并包扎，术毕安返病房。
 3.术中出血约10ml，未输血。</t>
         </is>
       </c>
-      <c r="T84" s="6" t="inlineStr">
+      <c r="T84" s="5" t="inlineStr">
         <is>
           <t>2024-12-26 00:00</t>
         </is>
       </c>
-      <c r="U84" s="6" t="inlineStr">
+      <c r="U84" s="5" t="inlineStr">
         <is>
           <t>经腹盆腔穿刺引流术 | 腹腔镜下肠粘连松解术 | 腹腔镜胃修补术</t>
         </is>
       </c>
-      <c r="V84" s="6" t="inlineStr">
+      <c r="V84" s="5" t="inlineStr">
         <is>
           <t>阵发性脐周腹痛9小时</t>
         </is>
       </c>
-      <c r="W84" s="6" t="inlineStr">
+      <c r="W84" s="5" t="inlineStr">
         <is>
           <t>9小时前无明显诱因患儿出现阵发性脐周腹痛，无恶心呕吐，不伴发热，无尿频、尿急、尿痛及腰痛等不适。否认不洁饮食史，否认腹部外伤史，否认近期做过剧烈运动。否认在外院治疗。今来我院门诊就诊，以“腹痛待查”收入院。         患儿自发病以来，精神食欲睡眠可，小便正常}，大便正常。</t>
         </is>
       </c>
-      <c r="X84" s="6" t="inlineStr">
+      <c r="X84" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y84" s="6" t="inlineStr"/>
-      <c r="Z84" s="6" t="inlineStr"/>
-      <c r="AA84" s="6" t="inlineStr">
+      <c r="Y84" s="5" t="inlineStr"/>
+      <c r="Z84" s="5" t="inlineStr"/>
+      <c r="AA84" s="5" t="inlineStr">
         <is>
           <t>?6其他/待读</t>
         </is>
       </c>
-      <c r="AB84" s="6" t="inlineStr"/>
-      <c r="AC84" s="6" t="inlineStr"/>
-      <c r="AD84" s="6" t="inlineStr"/>
-      <c r="AE84" s="6" t="inlineStr"/>
-      <c r="AF84" s="6" t="inlineStr"/>
-      <c r="AG84" s="6" t="inlineStr"/>
-      <c r="AH84" s="6" t="inlineStr"/>
-      <c r="AI84" s="6" t="inlineStr"/>
-      <c r="AJ84" s="6" t="inlineStr"/>
-      <c r="AK84" s="6" t="inlineStr"/>
-      <c r="AL84" s="6" t="inlineStr"/>
-      <c r="AM84" s="6" t="inlineStr"/>
-      <c r="AN84" s="6" t="inlineStr"/>
-      <c r="AO84" s="6" t="inlineStr"/>
-      <c r="AP84" s="6" t="inlineStr"/>
-      <c r="AQ84" s="6" t="inlineStr"/>
+      <c r="AB84" s="5" t="inlineStr"/>
+      <c r="AC84" s="5" t="inlineStr"/>
+      <c r="AD84" s="5" t="inlineStr"/>
+      <c r="AE84" s="5" t="inlineStr"/>
+      <c r="AF84" s="5" t="inlineStr"/>
+      <c r="AG84" s="5" t="inlineStr"/>
+      <c r="AH84" s="5" t="inlineStr"/>
+      <c r="AI84" s="5" t="inlineStr"/>
+      <c r="AJ84" s="5" t="inlineStr"/>
+      <c r="AK84" s="5" t="inlineStr"/>
+      <c r="AL84" s="5" t="inlineStr"/>
+      <c r="AM84" s="5" t="inlineStr"/>
+      <c r="AN84" s="5" t="inlineStr"/>
+      <c r="AO84" s="5" t="inlineStr"/>
+      <c r="AP84" s="5" t="inlineStr"/>
+      <c r="AQ84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12860,488 +12876,488 @@
       <c r="AQ85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n">
+      <c r="A86" s="5" t="n">
         <v>35831035</v>
       </c>
-      <c r="B86" s="6" t="n">
+      <c r="B86" s="5" t="n">
         <v>101650712</v>
       </c>
-      <c r="C86" s="6" t="n">
+      <c r="C86" s="5" t="n">
         <v>2464311</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录+无出院小结</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>女性</t>
         </is>
       </c>
-      <c r="G86" s="6" t="n">
+      <c r="G86" s="5" t="n">
         <v>8.42</v>
       </c>
-      <c r="H86" s="6" t="n">
+      <c r="H86" s="5" t="n">
         <v>3074</v>
       </c>
-      <c r="I86" s="6" t="inlineStr">
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J86" s="6" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="K86" s="6" t="n">
+      <c r="K86" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="L86" s="6" t="n">
+      <c r="L86" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="M86" s="6" t="inlineStr">
+      <c r="M86" s="5" t="inlineStr">
         <is>
           <t>小儿消化内科二病区</t>
         </is>
       </c>
-      <c r="N86" s="6" t="inlineStr">
+      <c r="N86" s="5" t="inlineStr">
         <is>
           <t>腹痛</t>
         </is>
       </c>
-      <c r="O86" s="6" t="inlineStr">
+      <c r="O86" s="5" t="inlineStr">
         <is>
           <t>十二指肠溃疡</t>
         </is>
       </c>
-      <c r="P86" s="6" t="inlineStr">
+      <c r="P86" s="5" t="inlineStr">
         <is>
           <t>十二指肠溃疡 | 十二指肠穿孔 | 幽门螺旋杆菌感染 | 心电图异常</t>
         </is>
       </c>
-      <c r="Q86" s="6" t="inlineStr"/>
-      <c r="R86" s="6" t="inlineStr"/>
-      <c r="S86" s="6" t="inlineStr"/>
-      <c r="T86" s="6" t="inlineStr"/>
-      <c r="U86" s="6" t="inlineStr"/>
-      <c r="V86" s="6" t="inlineStr">
+      <c r="Q86" s="5" t="inlineStr"/>
+      <c r="R86" s="5" t="inlineStr"/>
+      <c r="S86" s="5" t="inlineStr"/>
+      <c r="T86" s="5" t="inlineStr"/>
+      <c r="U86" s="5" t="inlineStr"/>
+      <c r="V86" s="5" t="inlineStr">
         <is>
           <t>间断腹痛1年余，加重1天</t>
         </is>
       </c>
-      <c r="W86" s="6" t="inlineStr">
+      <c r="W86" s="5" t="inlineStr">
         <is>
           <t>患儿1年余前无明显诱因出现腹痛，脐周为主，阵发性隐痛为主，持续几分钟自行缓解，程度尚可忍受，日间为主，无夜间痛醒，与进食无明显相关，无恶心呕吐，无皮疹，无关节肿痛，无尿少浮肿，无发热，无头晕头痛，平均每年发作4-5次，每次腹痛持续4-5天，多次于外院及我院门诊就诊，予“肚脐贴、对症中成药物”治疗后缓解，家属诉每次“血常规提示白细胞升高”，后未再复查；腹痛缓解期间无腹痛，无呕吐腹泻等；4天前再次出现腹痛，性质同前，1天前较前加重，程度较前加剧，不能忍受，持续几分钟后缓解，无呕吐腹泻，无便秘，腹痛时伴测得体温37.5℃，体温可自行降至正常，无咳嗽流涕，为进一步诊治今日来我院门诊就诊，完善腹部CT提示“胃幽门至十二指肠降段肠壁水肿增厚，周围间隙积液；胆囊窝积液；肠系膜部分淋巴结大，盆腔积液”，门诊以“腹痛”收入院。         自起病以来，精神睡眠尚可，腹痛时食欲欠佳，缓解时食欲尚可，大小便未见异常，体重无明显下降。</t>
         </is>
       </c>
-      <c r="X86" s="6" t="inlineStr">
+      <c r="X86" s="5" t="inlineStr">
         <is>
           <t>平时健康情况:一般          疾病史:无疾病史         传染病史：否认传染病史</t>
         </is>
       </c>
-      <c r="Y86" s="6" t="inlineStr"/>
-      <c r="Z86" s="6" t="inlineStr"/>
-      <c r="AA86" s="6" t="inlineStr">
+      <c r="Y86" s="5" t="inlineStr"/>
+      <c r="Z86" s="5" t="inlineStr"/>
+      <c r="AA86" s="5" t="inlineStr">
         <is>
           <t>?3消化性溃疡</t>
         </is>
       </c>
-      <c r="AB86" s="6" t="inlineStr"/>
-      <c r="AC86" s="6" t="inlineStr"/>
-      <c r="AD86" s="6" t="inlineStr"/>
-      <c r="AE86" s="6" t="inlineStr"/>
-      <c r="AF86" s="6" t="inlineStr"/>
-      <c r="AG86" s="6" t="inlineStr"/>
-      <c r="AH86" s="6" t="inlineStr"/>
-      <c r="AI86" s="6" t="inlineStr"/>
-      <c r="AJ86" s="6" t="inlineStr"/>
-      <c r="AK86" s="6" t="inlineStr"/>
-      <c r="AL86" s="6" t="inlineStr"/>
-      <c r="AM86" s="6" t="inlineStr"/>
-      <c r="AN86" s="6" t="inlineStr"/>
-      <c r="AO86" s="6" t="inlineStr"/>
-      <c r="AP86" s="6" t="inlineStr"/>
-      <c r="AQ86" s="6" t="inlineStr"/>
+      <c r="AB86" s="5" t="inlineStr"/>
+      <c r="AC86" s="5" t="inlineStr"/>
+      <c r="AD86" s="5" t="inlineStr"/>
+      <c r="AE86" s="5" t="inlineStr"/>
+      <c r="AF86" s="5" t="inlineStr"/>
+      <c r="AG86" s="5" t="inlineStr"/>
+      <c r="AH86" s="5" t="inlineStr"/>
+      <c r="AI86" s="5" t="inlineStr"/>
+      <c r="AJ86" s="5" t="inlineStr"/>
+      <c r="AK86" s="5" t="inlineStr"/>
+      <c r="AL86" s="5" t="inlineStr"/>
+      <c r="AM86" s="5" t="inlineStr"/>
+      <c r="AN86" s="5" t="inlineStr"/>
+      <c r="AO86" s="5" t="inlineStr"/>
+      <c r="AP86" s="5" t="inlineStr"/>
+      <c r="AQ86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n">
+      <c r="A87" s="5" t="n">
         <v>35856424</v>
       </c>
-      <c r="B87" s="6" t="n">
+      <c r="B87" s="5" t="n">
         <v>101660395</v>
       </c>
-      <c r="C87" s="6" t="n">
+      <c r="C87" s="5" t="n">
         <v>2474569</v>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G87" s="6" t="n">
+      <c r="G87" s="5" t="n">
         <v>12.82</v>
       </c>
-      <c r="H87" s="6" t="n">
+      <c r="H87" s="5" t="n">
         <v>4683</v>
       </c>
-      <c r="I87" s="6" t="inlineStr">
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J87" s="6" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="K87" s="6" t="n">
+      <c r="K87" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="L87" s="6" t="n">
+      <c r="L87" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="M87" s="6" t="inlineStr">
+      <c r="M87" s="5" t="inlineStr">
         <is>
           <t>肝胆外科/肿瘤外科病区</t>
         </is>
       </c>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="N87" s="5" t="inlineStr">
         <is>
           <t>消化道穿孔</t>
         </is>
       </c>
-      <c r="O87" s="6" t="inlineStr">
+      <c r="O87" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P87" s="6" t="inlineStr">
+      <c r="P87" s="5" t="inlineStr">
         <is>
           <t>胃穿孔 | 局限性腹膜炎 | 肠粘连 | 腹腔积液</t>
         </is>
       </c>
-      <c r="Q87" s="6" t="inlineStr">
+      <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>胃穿孔,局限性腹膜炎,腹腔积液,肠粘连</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
+      <c r="R87" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃修补术+腹腔镜下肠粘连松解术+经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="S87" s="6" t="inlineStr">
+      <c r="S87" s="5" t="inlineStr">
         <is>
           <t>1、患儿仰卧位，头稍抬高，监视器放于患儿头侧。麻醉满意后手术区域常规消毒铺巾，上导尿管顺利。2、首先在脐左、右侧行纵行各切开5mm、5mm，分别置入5mm、5mm Ttrocar 形成人工气腹，气腹压力10mmHg，再于右上腹腋前线肋缘下下置入5mm Ttrocar。3、探查腹腔见胃小弯处胃窦部大网膜粘连，附近可见脓性渗液，掀开大网膜可见胃窦部一处穿孔，穿孔部位大小约1.5cm*1.5cm,大网膜包裹，继续探查可见左侧结肠旁沟及盆腔约30ml脓性液体，吸取少量脓液送培养，周围肠管轻微粘连，钝性分离粘连，探查余肠管未见明显异常。4、2-0丝线8字全层缝合前壁穿孔部位，间断全层缝合穿孔部位加固，分别打结。温盐水冲洗腹腔。吸出残余积液，于盆腔各置引流管一条，妥善固定。5、解除气腹，拔出Trocar，对合伤口皮肤，5-0可吸收外科缝线缝合5.0mm切口皮下，医用组织胶粘合予以包扎。6、术中出血约2ml，尿量约400ml。术毕，安返病房。</t>
         </is>
       </c>
-      <c r="T87" s="6" t="inlineStr">
+      <c r="T87" s="5" t="inlineStr">
         <is>
           <t>2025-02-01 00:00</t>
         </is>
       </c>
-      <c r="U87" s="6" t="inlineStr">
+      <c r="U87" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃修补术 | 经腹盆腔穿刺引流术 | 腹腔镜下肠粘连松解术</t>
         </is>
       </c>
-      <c r="V87" s="6" t="inlineStr">
+      <c r="V87" s="5" t="inlineStr">
         <is>
           <t>持续性右腹腹痛5小时</t>
         </is>
       </c>
-      <c r="W87" s="6" t="inlineStr">
+      <c r="W87" s="5" t="inlineStr">
         <is>
           <t>5小时前无明显诱因患儿出现持续性右腹腹痛，不伴发热、呕吐、腹泻，无尿频、尿急、尿痛及腰痛等不适。否认不洁饮食史，否认腹部外伤史，否认近期做过剧烈运动。曾在通城县任命医院行腹部CT示腹腔游离气体，考虑腹部空腔脏器穿孔？。今来我院急诊就诊，以“消化道穿孔”收入院。         患儿自发病以来，精神食欲睡眠可，小便正常}，大便正常。</t>
         </is>
       </c>
-      <c r="X87" s="6" t="inlineStr">
+      <c r="X87" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y87" s="6" t="inlineStr"/>
-      <c r="Z87" s="6" t="inlineStr"/>
-      <c r="AA87" s="6" t="inlineStr">
+      <c r="Y87" s="5" t="inlineStr"/>
+      <c r="Z87" s="5" t="inlineStr"/>
+      <c r="AA87" s="5" t="inlineStr">
         <is>
           <t>?6其他/待读</t>
         </is>
       </c>
-      <c r="AB87" s="6" t="inlineStr"/>
-      <c r="AC87" s="6" t="inlineStr"/>
-      <c r="AD87" s="6" t="inlineStr"/>
-      <c r="AE87" s="6" t="inlineStr"/>
-      <c r="AF87" s="6" t="inlineStr"/>
-      <c r="AG87" s="6" t="inlineStr"/>
-      <c r="AH87" s="6" t="inlineStr"/>
-      <c r="AI87" s="6" t="inlineStr"/>
-      <c r="AJ87" s="6" t="inlineStr"/>
-      <c r="AK87" s="6" t="inlineStr"/>
-      <c r="AL87" s="6" t="inlineStr"/>
-      <c r="AM87" s="6" t="inlineStr"/>
-      <c r="AN87" s="6" t="inlineStr"/>
-      <c r="AO87" s="6" t="inlineStr"/>
-      <c r="AP87" s="6" t="inlineStr"/>
-      <c r="AQ87" s="6" t="inlineStr"/>
+      <c r="AB87" s="5" t="inlineStr"/>
+      <c r="AC87" s="5" t="inlineStr"/>
+      <c r="AD87" s="5" t="inlineStr"/>
+      <c r="AE87" s="5" t="inlineStr"/>
+      <c r="AF87" s="5" t="inlineStr"/>
+      <c r="AG87" s="5" t="inlineStr"/>
+      <c r="AH87" s="5" t="inlineStr"/>
+      <c r="AI87" s="5" t="inlineStr"/>
+      <c r="AJ87" s="5" t="inlineStr"/>
+      <c r="AK87" s="5" t="inlineStr"/>
+      <c r="AL87" s="5" t="inlineStr"/>
+      <c r="AM87" s="5" t="inlineStr"/>
+      <c r="AN87" s="5" t="inlineStr"/>
+      <c r="AO87" s="5" t="inlineStr"/>
+      <c r="AP87" s="5" t="inlineStr"/>
+      <c r="AQ87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="n">
+      <c r="A88" s="5" t="n">
         <v>35864333</v>
       </c>
-      <c r="B88" s="6" t="n">
+      <c r="B88" s="5" t="n">
         <v>101662946</v>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C88" s="5" t="n">
         <v>2477299</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G88" s="6" t="n">
+      <c r="G88" s="5" t="n">
         <v>12.25</v>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H88" s="5" t="n">
         <v>4476</v>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J88" s="6" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>2025-02-10</t>
         </is>
       </c>
-      <c r="K88" s="6" t="n">
+      <c r="K88" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="L88" s="6" t="n">
+      <c r="L88" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="M88" s="6" t="inlineStr">
+      <c r="M88" s="5" t="inlineStr">
         <is>
           <t>肝胆外科/肿瘤外科病区</t>
         </is>
       </c>
-      <c r="N88" s="6" t="inlineStr">
+      <c r="N88" s="5" t="inlineStr">
         <is>
           <t>消化道穿孔</t>
         </is>
       </c>
-      <c r="O88" s="6" t="inlineStr">
+      <c r="O88" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P88" s="6" t="inlineStr">
+      <c r="P88" s="5" t="inlineStr">
         <is>
           <t>胃穿孔 | 肠粘连 | 腹腔积液 | 局限性腹膜炎 | 幽门螺旋杆菌感染</t>
         </is>
       </c>
-      <c r="Q88" s="6" t="inlineStr">
+      <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>胃穿孔,肠粘连,腹腔积液,局限性腹膜炎</t>
         </is>
       </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="R88" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃修补术+腹腔镜下肠粘连松解术+经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="S88" s="6" t="inlineStr">
+      <c r="S88" s="5" t="inlineStr">
         <is>
           <t>1、患儿仰卧位，头稍抬高，监视器放于患儿头侧。麻醉满意后手术区域常规消毒铺巾，上导尿管顺利。2、首先在脐两侧各切开5mm、5mm，开放式置入5mm Ttrocar 形成人工气腹，气腹压力12mmHg，再于右脐旁腹直肌外缘处下置入5mm Ttrocar。3、探查腹腔见胃小弯处胃窦部大网膜、肠管及肝脏及胆囊粘连，附近可见脓性渗液，钝性分离粘连，可见胃小弯胃窦一处穿孔，穿孔部位大小约1.5cm*1.5cm,大网膜包裹，继续探查可见左侧结肠旁沟及盆腔约20ml脓性液体，吸取少量脓液送培养，余肠管未见明显异常。4、在剑突下方肝镰状韧带的左侧经腹壁穿入2-0医用缝合线，悬吊肝圆韧带，肝脏上提显露胃小弯胃窦部。2-0丝线全层缝合穿孔部位，间断全层缝合穿孔部位一针加固，分别打结。将大网膜覆盖至穿孔部位并用丝线固定。温盐水冲洗腹腔。吸出残余积液，于肝下置引流管一条，妥善固定。5、解除气腹，拔出Trocar，对合伤口皮肤，5-0可吸收外科缝线缝合5.0mm切口皮下，医用组织胶粘合予以包扎。6、术中出血约5ml，尿量约200ml。术毕，安返病房。</t>
         </is>
       </c>
-      <c r="T88" s="6" t="inlineStr">
+      <c r="T88" s="5" t="inlineStr">
         <is>
           <t>2025-02-10 00:00</t>
         </is>
       </c>
-      <c r="U88" s="6" t="inlineStr">
+      <c r="U88" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃修补术 | 腹腔镜下肠粘连松解术 | 经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="V88" s="6" t="inlineStr">
+      <c r="V88" s="5" t="inlineStr">
         <is>
           <t>剑突下疼痛腹胀1月余，间断性剑突下腹痛1天伴发热</t>
         </is>
       </c>
-      <c r="W88" s="6" t="inlineStr">
+      <c r="W88" s="5" t="inlineStr">
         <is>
           <t>1月余前无明显诱因出现剑突下疼痛伴腹胀，多为餐后半小时左右，自行口服铝镁加口服液后好转，1天前无明显诱因患儿出现间断性剑突下腹痛，为针刺样疼痛，后自行缓解，伴发热，最高体温38.6℃，自行降至正常；伴双侧颈部酸胀，不伴呕吐腹泻，无尿频、尿急、尿痛及腰痛等不适。否认不洁饮食史，否认腹部外伤史，否认近期做过剧烈运动。否认在外院治疗。今来我院门诊就诊，以“消化道穿孔”收入院。         患儿自发病以来，精神食欲睡眠欠佳，小便正常}，大便正常。</t>
         </is>
       </c>
-      <c r="X88" s="6" t="inlineStr">
+      <c r="X88" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y88" s="6" t="inlineStr"/>
-      <c r="Z88" s="6" t="inlineStr"/>
-      <c r="AA88" s="6" t="inlineStr">
+      <c r="Y88" s="5" t="inlineStr"/>
+      <c r="Z88" s="5" t="inlineStr"/>
+      <c r="AA88" s="5" t="inlineStr">
         <is>
           <t>?3消化性溃疡</t>
         </is>
       </c>
-      <c r="AB88" s="6" t="inlineStr"/>
-      <c r="AC88" s="6" t="inlineStr"/>
-      <c r="AD88" s="6" t="inlineStr"/>
-      <c r="AE88" s="6" t="inlineStr"/>
-      <c r="AF88" s="6" t="inlineStr"/>
-      <c r="AG88" s="6" t="inlineStr"/>
-      <c r="AH88" s="6" t="inlineStr"/>
-      <c r="AI88" s="6" t="inlineStr"/>
-      <c r="AJ88" s="6" t="inlineStr"/>
-      <c r="AK88" s="6" t="inlineStr"/>
-      <c r="AL88" s="6" t="inlineStr"/>
-      <c r="AM88" s="6" t="inlineStr"/>
-      <c r="AN88" s="6" t="inlineStr"/>
-      <c r="AO88" s="6" t="inlineStr"/>
-      <c r="AP88" s="6" t="inlineStr"/>
-      <c r="AQ88" s="6" t="inlineStr"/>
+      <c r="AB88" s="5" t="inlineStr"/>
+      <c r="AC88" s="5" t="inlineStr"/>
+      <c r="AD88" s="5" t="inlineStr"/>
+      <c r="AE88" s="5" t="inlineStr"/>
+      <c r="AF88" s="5" t="inlineStr"/>
+      <c r="AG88" s="5" t="inlineStr"/>
+      <c r="AH88" s="5" t="inlineStr"/>
+      <c r="AI88" s="5" t="inlineStr"/>
+      <c r="AJ88" s="5" t="inlineStr"/>
+      <c r="AK88" s="5" t="inlineStr"/>
+      <c r="AL88" s="5" t="inlineStr"/>
+      <c r="AM88" s="5" t="inlineStr"/>
+      <c r="AN88" s="5" t="inlineStr"/>
+      <c r="AO88" s="5" t="inlineStr"/>
+      <c r="AP88" s="5" t="inlineStr"/>
+      <c r="AQ88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="n">
+      <c r="A89" s="5" t="n">
         <v>35897928</v>
       </c>
-      <c r="B89" s="6" t="n">
+      <c r="B89" s="5" t="n">
         <v>101673363</v>
       </c>
-      <c r="C89" s="6" t="n">
+      <c r="C89" s="5" t="n">
         <v>2488565</v>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G89" s="6" t="n">
+      <c r="G89" s="5" t="n">
         <v>3.19</v>
       </c>
-      <c r="H89" s="6" t="n">
+      <c r="H89" s="5" t="n">
         <v>1164</v>
       </c>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>4学龄前</t>
         </is>
       </c>
-      <c r="J89" s="6" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="K89" s="6" t="n">
+      <c r="K89" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="L89" s="6" t="n">
+      <c r="L89" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="M89" s="6" t="inlineStr">
+      <c r="M89" s="5" t="inlineStr">
         <is>
           <t>重症医学科病区</t>
         </is>
       </c>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="N89" s="5" t="inlineStr">
         <is>
           <t>胃穿孔(术后)</t>
         </is>
       </c>
-      <c r="O89" s="6" t="inlineStr">
+      <c r="O89" s="5" t="inlineStr">
         <is>
           <t>脓毒血症</t>
         </is>
       </c>
-      <c r="P89" s="6" t="inlineStr">
+      <c r="P89" s="5" t="inlineStr">
         <is>
           <t>化脓性腹膜炎 | 胃穿孔 | 低蛋白血症 | 转氨酶升高 | 低钙血症 | 凝血功能异常 | 低丙种球蛋白血症 | 肾功能检查的异常结果 | 低钾血症 | 胸腔积液 | 肝内胆管结石 | 心肌酶谱异常 | 脓毒血症</t>
         </is>
       </c>
-      <c r="Q89" s="6" t="inlineStr"/>
-      <c r="R89" s="6" t="inlineStr"/>
-      <c r="S89" s="6" t="inlineStr"/>
-      <c r="T89" s="6" t="inlineStr"/>
-      <c r="U89" s="6" t="inlineStr"/>
-      <c r="V89" s="6" t="inlineStr">
+      <c r="Q89" s="5" t="inlineStr"/>
+      <c r="R89" s="5" t="inlineStr"/>
+      <c r="S89" s="5" t="inlineStr"/>
+      <c r="T89" s="5" t="inlineStr"/>
+      <c r="U89" s="5" t="inlineStr"/>
+      <c r="V89" s="5" t="inlineStr">
         <is>
           <t>呕吐腹痛2天，发热1天</t>
         </is>
       </c>
-      <c r="W89" s="6" t="inlineStr">
+      <c r="W89" s="5" t="inlineStr">
         <is>
           <t>患儿2天前（03.20）无明显诱因出现腹痛，具体部位及性质不详，伴进食后呕吐呕吐胃内容物，量少，非喷射性，无胆汁及咖啡渣样物质，约30-50次/天，伴烦吵、口渴，精神反应一般，至随州市妇幼保健院就诊，腹部彩超示肠系膜淋巴结炎，予护胃治疗后患儿症状稍缓解，03.21患儿出现发热，最高体温38.7℃，热峰2-3次/天，遂至随州市中心医院就诊，完善影象学检查考虑消化道穿孔，行急诊开腹探查，术中见胃穿孔，腹腔大量脓液，行胃修补术，反复冲洗腹腔后转入ICU治疗，余抗感染（具体不详）、补液等支持治疗，为求进一步诊治，携气管插管呼吸机辅助通气转入我院。         起病来，患儿饮食差，精神反应一般，大便3天未解，小便量较前减少。</t>
         </is>
       </c>
-      <c r="X89" s="6" t="inlineStr">
+      <c r="X89" s="5" t="inlineStr">
         <is>
           <t>平时健康情况:一般          疾病史:有疾病史，2024年心脏彩超示轻度三尖瓣返流         传染病史：否认传染病史</t>
         </is>
       </c>
-      <c r="Y89" s="6" t="inlineStr">
+      <c r="Y89" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神食欲睡眠好，无腹痛，无呕吐，无发热，大便正常，小便正常。查体：神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。</t>
         </is>
       </c>
-      <c r="Z89" s="6" t="inlineStr">
+      <c r="Z89" s="5" t="inlineStr">
         <is>
           <t>呕吐腹痛2天，发热1天，患者既往平时健康情况：一般，疾病史：有疾病史，2024年心脏彩超示轻度三尖瓣返流，外伤史：有外伤史：家长诉03.18摔伤，头部腹部受到撞击 过敏史：无，体温37.2℃，呼吸27次/分，规则，脉搏167次/分，血压120/76mmHg，体重13Kg ，身长96.0cm，发育良好，营养正常，神志嗜睡，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜无黄染，瞳孔等圆等大2.5mm，瞳孔对光反射正常，唇红润，咽气管插管中，扁桃体气管插管中，呼吸音粗，未闻及肺部啰音，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，伤口敷料清洁干燥，带入引流管引流通畅，肝脏未做，脾脏未做，未触及腹部包块，肠鸣音正常，脊柱生理弯曲存在，无病理性畸形，Kerning征阴性，Brudzinski征阴性。  患儿带入气管插管，镇静状态，胃管引流通畅，可见3个腹腔引流管（肝下、脾旁、盆腔）引流通畅，手术伤口敷料清洁干燥，尿管引流通畅，CRT 2-3s 随州市中心医院 03.21 血常规： WBC 18.03×10*9/L，N 15.18×10*9/L，L 10.6%，HGB 146g/L，PLT 390×10*9/L。、CRP 7.8mg/L、CT：考虑消化道穿孔（未见报告）  入院后完善相关检查，持续心电监测，呼吸机辅助通气（3.22-3.23），拔管后改为双鼻导管吸氧，给予美罗培南+万古霉素抗感染（3.22-3.27），酚磺乙胺、蝮蛇血凝酶止血，乌司他丁抗炎，并输注丙球（5g/天，3.24-3.25）,白蛋白（10g/次，3.22-3.24）、血浆（3.22）,予禁食，静脉营养支持治疗。现患儿病情稳定，请我科会诊后转我科进一步治疗，予以美罗培南(3.27-4.10)、万古霉素（3.27-4.7）继续抗感染治疗，复查;2025-04-09  血液分析五分类（血常规)（静脉血）:白细胞计数 3.55(10^9/L)↓，血红蛋白浓度 105(g/L)↓，红细胞计数 3.99(10^12/L)↓；2025-04-09  血浆凝血机制（6项）测定:D-二聚体 2.41(mg/L FEU)↑；2025-04-09  血清降钙素原(PCT)定量测定:降钙素原 0.060(ng/ml)↑；2025-04-09  血清肾功能5项（BUN、Cr、UA、Cys-C、RBP)测定:尿酸 197.0(μmol/L)↓；2025-04-09  血清肝功能11项测定:前白蛋白 175.0(mg/L)↓；2025-04-09  血清超敏C反应蛋白（hs-CRP)测定:超敏C反应蛋白 2.62(mg/L)；未见明显异常，2025-04-09 胃肠道彩超,肠积气。炎症指标较前明显好转，未诉腹痛不适，今病情稳定，临床治愈，征得家长同意，予以出院。</t>
         </is>
       </c>
-      <c r="AA89" s="6" t="inlineStr">
+      <c r="AA89" s="5" t="inlineStr">
         <is>
           <t>?6其他/待读</t>
         </is>
       </c>
-      <c r="AB89" s="6" t="inlineStr"/>
-      <c r="AC89" s="6" t="inlineStr"/>
-      <c r="AD89" s="6" t="inlineStr"/>
-      <c r="AE89" s="6" t="inlineStr"/>
-      <c r="AF89" s="6" t="inlineStr"/>
-      <c r="AG89" s="6" t="inlineStr"/>
-      <c r="AH89" s="6" t="inlineStr"/>
-      <c r="AI89" s="6" t="inlineStr"/>
-      <c r="AJ89" s="6" t="inlineStr"/>
-      <c r="AK89" s="6" t="inlineStr"/>
-      <c r="AL89" s="6" t="inlineStr"/>
-      <c r="AM89" s="6" t="inlineStr"/>
-      <c r="AN89" s="6" t="inlineStr"/>
-      <c r="AO89" s="6" t="inlineStr"/>
-      <c r="AP89" s="6" t="inlineStr"/>
-      <c r="AQ89" s="6" t="inlineStr"/>
+      <c r="AB89" s="5" t="inlineStr"/>
+      <c r="AC89" s="5" t="inlineStr"/>
+      <c r="AD89" s="5" t="inlineStr"/>
+      <c r="AE89" s="5" t="inlineStr"/>
+      <c r="AF89" s="5" t="inlineStr"/>
+      <c r="AG89" s="5" t="inlineStr"/>
+      <c r="AH89" s="5" t="inlineStr"/>
+      <c r="AI89" s="5" t="inlineStr"/>
+      <c r="AJ89" s="5" t="inlineStr"/>
+      <c r="AK89" s="5" t="inlineStr"/>
+      <c r="AL89" s="5" t="inlineStr"/>
+      <c r="AM89" s="5" t="inlineStr"/>
+      <c r="AN89" s="5" t="inlineStr"/>
+      <c r="AO89" s="5" t="inlineStr"/>
+      <c r="AP89" s="5" t="inlineStr"/>
+      <c r="AQ89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13665,146 +13681,146 @@
       <c r="AQ91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n">
+      <c r="A92" s="5" t="n">
         <v>35917881</v>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B92" s="5" t="n">
         <v>101687678</v>
       </c>
-      <c r="C92" s="6" t="n">
+      <c r="C92" s="5" t="n">
         <v>2504789</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>⚠第2次住院</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G92" s="5" t="n">
         <v>8.26</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H92" s="5" t="n">
         <v>3018</v>
       </c>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J92" s="6" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="K92" s="6" t="n">
+      <c r="K92" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="L92" s="6" t="n">
+      <c r="L92" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="M92" s="6" t="inlineStr">
+      <c r="M92" s="5" t="inlineStr">
         <is>
           <t>胃肠外科病区</t>
         </is>
       </c>
-      <c r="N92" s="6" t="inlineStr">
+      <c r="N92" s="5" t="inlineStr">
         <is>
           <t>多发性消化道异物</t>
         </is>
       </c>
-      <c r="O92" s="6" t="inlineStr">
+      <c r="O92" s="5" t="inlineStr">
         <is>
           <t>消化道内异物</t>
         </is>
       </c>
-      <c r="P92" s="6" t="inlineStr">
+      <c r="P92" s="5" t="inlineStr">
         <is>
           <t>消化道内异物 | 食管瘘 | 胃穿孔</t>
         </is>
       </c>
-      <c r="Q92" s="6" t="inlineStr">
+      <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>消化道内异物(磁铁6颗),食管瘘,胃穿孔(胃瘘)</t>
         </is>
       </c>
-      <c r="R92" s="6" t="inlineStr">
+      <c r="R92" s="5" t="inlineStr">
         <is>
           <t>胃镜检查+食管内异物去除+内镜下胃内异物去除+内镜下食管钛夹止血术</t>
         </is>
       </c>
-      <c r="S92" s="6" t="inlineStr">
+      <c r="S92" s="5" t="inlineStr">
         <is>
           <t>1.取左侧卧位，麻醉成功后经口置胃镜至食管下段可见成串磁铁残留，周围组织水肿增厚，检查见胃底原异物穿孔窦道残留位置已基本愈合。置入异物网兜，于食管下段套扎住异物，充分注气并退出胃镜，避免损伤消化道，成功取出异物。术中排拍片未见明显磁铁异物残留，局部可见少量锈迹残余。再次进镜检查：可见异物食管下段约0.8*0.5cm2窦道口，局部肉芽组织增生，局部冲洗和吸引窦道口，在食管下段予以2枚钛夹夹闭瘘口止血，反复检查未见明显出血，充分注气并退出胃镜，避免损伤消化道，尿量未计。
 2.术毕，患儿返病房。</t>
         </is>
       </c>
-      <c r="T92" s="6" t="inlineStr">
+      <c r="T92" s="5" t="inlineStr">
         <is>
           <t>2025-05-09 00:00</t>
         </is>
       </c>
-      <c r="U92" s="6" t="inlineStr">
+      <c r="U92" s="5" t="inlineStr">
         <is>
           <t>食管内异物去除 | 胃镜检查 | 内镜下胃内异物去除 | 内镜下胃钛夹止血术</t>
         </is>
       </c>
-      <c r="V92" s="6" t="inlineStr">
+      <c r="V92" s="5" t="inlineStr">
         <is>
           <t>误食异物27天</t>
         </is>
       </c>
-      <c r="W92" s="6" t="inlineStr">
+      <c r="W92" s="5" t="inlineStr">
         <is>
           <t>27天前患儿玩耍时不慎吞食异物，异物可能为6枚磁铁，无发热，进食或嗳气后伴胸痛，进食后呕吐1次，为胃内容物，呼出气体带铁锈味。外院行腹片提示消化道异物，后我院行胃镜检查提示异物位位于胃底及食管下端，磁珠相互吸引，予以放置空肠管，住院8天后无不适出院观察，现磁珠位置未见明显改变，为进一步治疗，今来我院门诊就诊，以"消化道异物"收入院。         患儿自发病以来，精神食欲睡眠一般，小便正常，大便2次，素有便秘，2-4天1次，大便较干结。</t>
         </is>
       </c>
-      <c r="X92" s="6" t="inlineStr">
+      <c r="X92" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y92" s="6" t="inlineStr">
+      <c r="Y92" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神食欲睡眠好，无腹痛，无呕吐，无发热，大便正常，小便正常。查体：T:36.8℃，P:90次/分，R:18次/分。神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。</t>
         </is>
       </c>
-      <c r="Z92" s="6" t="inlineStr">
+      <c r="Z92" s="5" t="inlineStr">
         <is>
           <t>误食异物27天，患者既往平时健康情况：一般，疾病史：无疾病史，外伤史：否认外伤史，过敏史：无，体温36.4℃，呼吸22次/分，规则，脉搏94次/分，规则，血压105/62mmHg，体重26.5Kg ，身长133.0cm，发育良好，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜无黄染，瞳孔等圆等大4mm，瞳孔对光反射正常，唇红润，扁桃体双侧无肿大，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率94次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，全腹柔软，无压痛，无反跳痛，肝脏肋下未触及，胆囊Murphy征阴性，脾脏肋下未触及，未触及腹部包块，移动性浊音呈阴性，肠鸣音正常，无肾区叩痛，四肢正常，，脊柱生理弯曲存在，无病理性畸形，病理反射无，Babinski征阴性。  鼻空肠管营养管在位通畅，腹部平坦，未见胃肠型；触：腹部软，全腹压痛阴性，反跳痛阴性，未扪及包块；叩：移动性浊音阴性；听：肠鸣音正常，4次/分； 2025-04-10 协和西院，腹片：消化道异物。2025-04-30 腹部立位(正侧位)X光片,“消化道异物”：与2025.4.21片比较，该异物位置无明显变化（食管下段、贲门区？）。  入院后完善相关检查，于2025/05/09 全麻下行内镜下胃内异物去除+内镜下胃钛夹止血术+食管内异物去除+胃镜检查，术中见胃底瘘愈合，食管侧瘘口予以钛夹夹闭，术后行护胃、止血、补液对症等治疗，现患儿径口饮食无不适，体温正常，术后行胸部CT未见明显感染灶形成，暂未见瘘管。今病情稳定，临床治愈，征得家长同意，予以出院。</t>
         </is>
       </c>
-      <c r="AA92" s="6" t="inlineStr">
+      <c r="AA92" s="5" t="inlineStr">
         <is>
           <t>?1异物相关</t>
         </is>
       </c>
-      <c r="AB92" s="6" t="inlineStr">
+      <c r="AB92" s="5" t="inlineStr">
         <is>
           <t>磁铁</t>
         </is>
       </c>
-      <c r="AC92" s="6" t="inlineStr"/>
-      <c r="AD92" s="6" t="inlineStr"/>
-      <c r="AE92" s="6" t="inlineStr"/>
-      <c r="AF92" s="6" t="inlineStr"/>
-      <c r="AG92" s="6" t="inlineStr"/>
-      <c r="AH92" s="6" t="inlineStr"/>
-      <c r="AI92" s="6" t="inlineStr"/>
-      <c r="AJ92" s="6" t="inlineStr"/>
-      <c r="AK92" s="6" t="inlineStr"/>
-      <c r="AL92" s="6" t="inlineStr"/>
-      <c r="AM92" s="6" t="inlineStr"/>
-      <c r="AN92" s="6" t="inlineStr"/>
-      <c r="AO92" s="6" t="inlineStr"/>
-      <c r="AP92" s="6" t="inlineStr"/>
-      <c r="AQ92" s="6" t="inlineStr"/>
+      <c r="AC92" s="5" t="inlineStr"/>
+      <c r="AD92" s="5" t="inlineStr"/>
+      <c r="AE92" s="5" t="inlineStr"/>
+      <c r="AF92" s="5" t="inlineStr"/>
+      <c r="AG92" s="5" t="inlineStr"/>
+      <c r="AH92" s="5" t="inlineStr"/>
+      <c r="AI92" s="5" t="inlineStr"/>
+      <c r="AJ92" s="5" t="inlineStr"/>
+      <c r="AK92" s="5" t="inlineStr"/>
+      <c r="AL92" s="5" t="inlineStr"/>
+      <c r="AM92" s="5" t="inlineStr"/>
+      <c r="AN92" s="5" t="inlineStr"/>
+      <c r="AO92" s="5" t="inlineStr"/>
+      <c r="AP92" s="5" t="inlineStr"/>
+      <c r="AQ92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -14080,198 +14096,198 @@
       <c r="AQ94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="n">
+      <c r="A95" s="5" t="n">
         <v>30810106</v>
       </c>
-      <c r="B95" s="6" t="n">
+      <c r="B95" s="5" t="n">
         <v>101705969</v>
       </c>
-      <c r="C95" s="6" t="n">
+      <c r="C95" s="5" t="n">
         <v>2527627</v>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>⚠无手术记录</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G95" s="6" t="n">
+      <c r="G95" s="5" t="n">
         <v>12.66</v>
       </c>
-      <c r="H95" s="6" t="n">
+      <c r="H95" s="5" t="n">
         <v>4625</v>
       </c>
-      <c r="I95" s="6" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J95" s="6" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="K95" s="6" t="n">
+      <c r="K95" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="L95" s="6" t="n">
+      <c r="L95" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="M95" s="6" t="inlineStr">
+      <c r="M95" s="5" t="inlineStr">
         <is>
           <t>小儿消化内科二病区</t>
         </is>
       </c>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="N95" s="5" t="inlineStr">
         <is>
           <t>腹痛</t>
         </is>
       </c>
-      <c r="O95" s="6" t="inlineStr">
+      <c r="O95" s="5" t="inlineStr">
         <is>
           <t>十二指肠穿孔</t>
         </is>
       </c>
-      <c r="P95" s="6" t="inlineStr">
+      <c r="P95" s="5" t="inlineStr">
         <is>
           <t>贫血 | 十二指肠穿孔 | 腹膜炎 | 胆囊炎 | 阑尾结石 | 下消化道出血 | 腹痛</t>
         </is>
       </c>
-      <c r="Q95" s="6" t="inlineStr"/>
-      <c r="R95" s="6" t="inlineStr"/>
-      <c r="S95" s="6" t="inlineStr"/>
-      <c r="T95" s="6" t="inlineStr"/>
-      <c r="U95" s="6" t="inlineStr"/>
-      <c r="V95" s="6" t="inlineStr">
+      <c r="Q95" s="5" t="inlineStr"/>
+      <c r="R95" s="5" t="inlineStr"/>
+      <c r="S95" s="5" t="inlineStr"/>
+      <c r="T95" s="5" t="inlineStr"/>
+      <c r="U95" s="5" t="inlineStr"/>
+      <c r="V95" s="5" t="inlineStr">
         <is>
           <t>间断腹痛1年，面色苍白半年，黑便3周伴腹痛加重2天</t>
         </is>
       </c>
-      <c r="W95" s="6" t="inlineStr">
+      <c r="W95" s="5" t="inlineStr">
         <is>
           <t>1年前患儿无明显诱因出现腹痛，上腹部为主，进食后为主，程度时轻时重，可耐受，持续时间不等，可自行缓解，无明显发作规律，无夜间痛醒，偶有反酸、嗳气，偶有饱胀，无血便、腹泻及便秘，无血尿，无发热，无黄疸，2024.05.03至我院就诊，予“阿莫西林克拉维酸钾、磷酸铝凝胶”口服1-2周，腹痛明显好转，6-8月期间未诉腹痛，半年前家长发现患儿面色苍白，呈进行性加重，伴有乏力，无头晕、心悸，无出血表现，伴间断腹痛，2025.05至当地中医院就诊，诊断为“中度贫血（未见血常规报告单）”，予“中药膏（不详）”口服1月（5月），无好转，再次至麻城市中医院就诊，予“右旋糖酐铁口服液、参苓白术健脾颗粒、维生素C”口服1月（6月），无好转，3周前患儿自诉伴解黑便，可见黄色粪渣（占比多），无头晕、黑曚，伴恶心，无晕厥、抽搐，病程中（1周前）伴有呕吐1次，喷射性，为胃内容物，不含咖啡渣样物质，无咳嗽、咯血等，无鼻衄、牙龈出现、皮肤黏膜瘀斑瘀点，无血尿等其他出血表现，无皮肤巩膜黄染，无皮疹，2天前腹痛明显加重，1-2次/天，每次持续1小时后平躺休息后自行缓解，有夜间痛醒，遂至我院门诊就诊，为进一步诊治，门诊以"腹痛、消化道出血、中度贫血、异常的体重减轻"收入院。         起病以来，患儿精神反应一般，食欲欠佳，体力下降，大便昨日未解，小便未见异常，近1年体重下          降7.5kg。</t>
         </is>
       </c>
-      <c r="X95" s="6" t="inlineStr">
+      <c r="X95" s="5" t="inlineStr">
         <is>
           <t>平时健康情况:一般          疾病史:无疾病史         传染病史：否认传染病史</t>
         </is>
       </c>
-      <c r="Y95" s="6" t="inlineStr">
+      <c r="Y95" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神食欲睡眠好，无腹痛，无呕吐，无发热，大便正常，小便正常。查体：T:36.2℃，P:88次/分，R:12次/分。神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。</t>
         </is>
       </c>
-      <c r="Z95" s="6" t="inlineStr">
+      <c r="Z95" s="5" t="inlineStr">
         <is>
           <t>间断腹痛1年，面色苍白半年，黑便3周伴腹痛加重2天，患者既往平时健康情况：一般，疾病史：无疾病史，外伤史：否认外伤史，过敏史：无，体温36.2℃，呼吸18次/分，规则，脉搏117次/分，规则，血压107/65mmHg，体重33Kg ，身长156.0cm，发育良好，营养正常，神志清楚，色泽苍白，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜无黄染，瞳孔等圆等大2.5mm，瞳孔对光反射正常，唇苍白，扁桃体左侧I°肿大 ，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率117次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，全腹柔软，上腹部轻压痛压痛，无反跳痛，肝脏肋下未触及，胆囊Murphy征阴性，脾脏肋下未触及，未触及腹部包块，移动性浊音呈阴性，肠鸣音正常，无肾区叩痛，四肢正常，四肢活动自如，脊柱生理弯曲存在，无病理性畸形，无病理反射，Kerning征阴性，Brudzinski征阴性。  神清反应可，皮肤弹性可，皮肤色泽苍白，无皮疹，唇苍白，扁桃体左侧I°肿大 ，咽无充血，全腹柔软，上腹部轻压痛，无反跳痛，肛周正常。 我院门诊：2025-07-06  末梢血超敏C反应蛋白(hsCRP)测定:超敏C反应蛋白 7.50(mg/L)↑；2025-07-06  血液分析五分类（血常规)（末梢血）:白细胞计数 13.17(10^9/L)↑，血小板压积 0.620(%)↑，血红蛋白浓度 83(g/L)↓，红细胞压积 30.4(%)↓，平均红细胞体积 71.4(fL)↓，平均红细胞血红蛋白量 18.3(pg)↓，平均红细胞血红蛋白浓度 257(g/L)↓，血小板计数 568(10^9/L)↑，淋巴细胞百分数 16.8(%)↓，中性粒细胞百分数 73.0(%)↑，淋巴细胞总数 2.21(10^9/L)，中性粒细胞总数 9.62(10^9/L)↑，单核细胞总数 1.17(10^9/L)↑，红细胞分布宽度 22.4(%)↑，红细胞体积分布宽度-SD 55.5(fL)↑，血小板分布宽度 12.2(%)↓，红细胞计数 4.26(10^12/L)↓；  入院后完善相关检查：2025-07-07  血清血脂六项测定:总胆固醇 2.63(mmol/L)↓，低密度脂蛋白胆固醇 1.35(mmol/L)↓，大致正常。2025-07-07  血清铁（FE)测定:铁 3.75(μmol/L)↓，铁缺乏，考虑贫血导致。2025-07-07  全血红细胞沉降率测定（血沉):血沉 1(mm/h)，大致正常。2025-07-06  血浆凝血机制（6项）测定:纤维蛋白原 4.40(g/L)↑，D-二聚体 1.11(mg/L FEU)↑。淀粉酶、心肌酶正常。2025-07-06  血清电解质6项（K 、Na、Cl、Ca、Mg、P)测定:钠 134.4(mmol/L)↓，氯 97.3(mmol/L)↓。肾功能、肝功能大致正常。2025-07-06 床边心电图检查(十二通道常规)+心电向量图,窦性心律;正常心电图;正常心电向量图。2025-07-06 胸部DR拍片(正侧位),双肺、心膈未见明显异常。2025-07-06 腹盆CT平扫（含体层成像及三维重建）,右上腹部异常改变，感染多考虑，建议增强检查；胆囊炎性改变；左上腹部分小肠肠壁增厚，肠系膜肿胀，部分结肠肠壁增厚；阑尾粪石2025-07-07 腹盆CT增强扫描+体层成像+三维重建：胃幽门至十二指肠球部移行处肠壁不连续，穿孔伴腹膜炎多考虑，胆囊壁及肝右叶局部受累；胆囊窝及肝下缘周围积液，盆腔积液。消化内科入院后予以予以头孢他啶抗感染，奥美拉唑抑酸护胃，巴曲亭止血补液对症支持治疗，完善腹盆CT增强检查提示穿孔伴腹膜炎多考虑，请我科医师会诊后建议转入我科继续治疗，取消胃肠镜。转入我科后，完善相关检查：2025-07-09  血检常规6项+CRP+网织红:红细胞计数 3.36(10^12/L)↓，血红蛋白浓度 64(g/L)↓，红细胞压积 22.1(%)↓，网织平均血红蛋白含量 17.2(pg)↓，超敏C反应蛋白 7.84(mg/L)↑。碳13呼气试验提示 DOB=20.7。2025-07-11  血清幽门螺旋杆菌（HP)芯片检测:细胞毒素相关蛋白 阳性（+）↑，尿素酶 阳性（+）↑，空泡毒素相关蛋白 阳性（+）↑；我科予以抗感染、止血、输血、护胃、保护胃黏膜、补铁补液等对症治疗。复查后肝肾功能电解质、超敏C反应蛋白、降钙素原未见明显异常。2025-07-14  血液分析五分类（血常规)（静脉血）:血红蛋白浓度 89(g/L)↓，红细胞压积 31.5(%)↓，平均红细胞体积 74.3(fL)↓，平均红细胞血红蛋白量 21.0(pg)↓，平均红细胞血红蛋白浓度 283(g/L)↓；今病情平稳，家长要求出院，告知风险及注意事项，签字予以出院。</t>
         </is>
       </c>
-      <c r="AA95" s="6" t="inlineStr">
+      <c r="AA95" s="5" t="inlineStr">
         <is>
           <t>?6其他/待读</t>
         </is>
       </c>
-      <c r="AB95" s="6" t="inlineStr"/>
-      <c r="AC95" s="6" t="inlineStr"/>
-      <c r="AD95" s="6" t="inlineStr"/>
-      <c r="AE95" s="6" t="inlineStr"/>
-      <c r="AF95" s="6" t="inlineStr"/>
-      <c r="AG95" s="6" t="inlineStr"/>
-      <c r="AH95" s="6" t="inlineStr"/>
-      <c r="AI95" s="6" t="inlineStr"/>
-      <c r="AJ95" s="6" t="inlineStr"/>
-      <c r="AK95" s="6" t="inlineStr"/>
-      <c r="AL95" s="6" t="inlineStr"/>
-      <c r="AM95" s="6" t="inlineStr"/>
-      <c r="AN95" s="6" t="inlineStr"/>
-      <c r="AO95" s="6" t="inlineStr"/>
-      <c r="AP95" s="6" t="inlineStr"/>
-      <c r="AQ95" s="6" t="inlineStr"/>
+      <c r="AB95" s="5" t="inlineStr"/>
+      <c r="AC95" s="5" t="inlineStr"/>
+      <c r="AD95" s="5" t="inlineStr"/>
+      <c r="AE95" s="5" t="inlineStr"/>
+      <c r="AF95" s="5" t="inlineStr"/>
+      <c r="AG95" s="5" t="inlineStr"/>
+      <c r="AH95" s="5" t="inlineStr"/>
+      <c r="AI95" s="5" t="inlineStr"/>
+      <c r="AJ95" s="5" t="inlineStr"/>
+      <c r="AK95" s="5" t="inlineStr"/>
+      <c r="AL95" s="5" t="inlineStr"/>
+      <c r="AM95" s="5" t="inlineStr"/>
+      <c r="AN95" s="5" t="inlineStr"/>
+      <c r="AO95" s="5" t="inlineStr"/>
+      <c r="AP95" s="5" t="inlineStr"/>
+      <c r="AQ95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="n">
+      <c r="A96" s="5" t="n">
         <v>36096190</v>
       </c>
-      <c r="B96" s="6" t="n">
+      <c r="B96" s="5" t="n">
         <v>101735136</v>
       </c>
-      <c r="C96" s="6" t="n">
+      <c r="C96" s="5" t="n">
         <v>2552105</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G96" s="6" t="n">
+      <c r="G96" s="5" t="n">
         <v>15.49</v>
       </c>
-      <c r="H96" s="6" t="n">
+      <c r="H96" s="5" t="n">
         <v>5656</v>
       </c>
-      <c r="I96" s="6" t="inlineStr">
+      <c r="I96" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J96" s="6" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>2025-09-16</t>
         </is>
       </c>
-      <c r="K96" s="6" t="n">
+      <c r="K96" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="L96" s="6" t="n">
+      <c r="L96" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="M96" s="6" t="inlineStr">
+      <c r="M96" s="5" t="inlineStr">
         <is>
           <t>肝胆外科/肿瘤外科病区</t>
         </is>
       </c>
-      <c r="N96" s="6" t="inlineStr">
+      <c r="N96" s="5" t="inlineStr">
         <is>
           <t>腹痛</t>
         </is>
       </c>
-      <c r="O96" s="6" t="inlineStr">
+      <c r="O96" s="5" t="inlineStr">
         <is>
           <t>十二指肠溃疡伴穿孔</t>
         </is>
       </c>
-      <c r="P96" s="6" t="inlineStr">
+      <c r="P96" s="5" t="inlineStr">
         <is>
           <t>胸腔积液 | 肺实变 | 十二指肠溃疡伴穿孔</t>
         </is>
       </c>
-      <c r="Q96" s="6" t="inlineStr">
+      <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>十二指肠溃疡穿孔</t>
         </is>
       </c>
-      <c r="R96" s="6" t="inlineStr">
+      <c r="R96" s="5" t="inlineStr">
         <is>
           <t>十二指肠溃疡穿孔修补术+腹腔镜检查+腹腔镜中转剖腹探查术</t>
         </is>
       </c>
-      <c r="S96" s="6" t="inlineStr">
+      <c r="S96" s="5" t="inlineStr">
         <is>
           <t>1、患儿仰卧位,监视器放于患儿头部右侧。麻醉满意后手术区域常规消毒铺巾，留置尿管顺利。
 2、首先在脐窝上行切开5mm，开放式置入5mm Ttrocar形成人工气腹，气腹压力12mmHg，插入腹腔镜，直视下分别于右上腹腋前线肋缘下、右锁骨中线平脐处置入5mm Ttrocar。
@@ -14281,54 +14297,54 @@
 6、逐层关腹，间断缝合皮肤。外用纱布加压包扎。术毕返ICU。术中出血200ml，尿量500ml。</t>
         </is>
       </c>
-      <c r="T96" s="6" t="inlineStr">
+      <c r="T96" s="5" t="inlineStr">
         <is>
           <t>2025-09-16 00:00</t>
         </is>
       </c>
-      <c r="U96" s="6" t="inlineStr">
+      <c r="U96" s="5" t="inlineStr">
         <is>
           <t>十二指肠溃疡穿孔修补术 | 腹腔镜检查 | 腹腔镜中转剖腹探查术</t>
         </is>
       </c>
-      <c r="V96" s="6" t="inlineStr">
+      <c r="V96" s="5" t="inlineStr">
         <is>
           <t>阵发性上腹腹痛1周</t>
         </is>
       </c>
-      <c r="W96" s="6" t="inlineStr">
+      <c r="W96" s="5" t="inlineStr">
         <is>
           <t>1周前患儿进食后出现阵发性上腹腹痛，不伴发热，当时于外院行抗炎治疗，治疗后腹痛明显好转，昨日进食后腹痛加重，于外院行CT检查提示十二指肠降部走行显示紊乱，可见小气泡影。后未予以特殊治疗，今来我院门诊就诊，行CT检查提示十二指肠穿孔，以“消化道穿孔”收入院。         患儿自发病以来，精神食欲睡眠欠佳，饮食较不规律，小便正常}，大便正常。</t>
         </is>
       </c>
-      <c r="X96" s="6" t="inlineStr">
+      <c r="X96" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y96" s="6" t="inlineStr"/>
-      <c r="Z96" s="6" t="inlineStr"/>
-      <c r="AA96" s="6" t="inlineStr">
+      <c r="Y96" s="5" t="inlineStr"/>
+      <c r="Z96" s="5" t="inlineStr"/>
+      <c r="AA96" s="5" t="inlineStr">
         <is>
           <t>?3消化性溃疡</t>
         </is>
       </c>
-      <c r="AB96" s="6" t="inlineStr"/>
-      <c r="AC96" s="6" t="inlineStr"/>
-      <c r="AD96" s="6" t="inlineStr"/>
-      <c r="AE96" s="6" t="inlineStr"/>
-      <c r="AF96" s="6" t="inlineStr"/>
-      <c r="AG96" s="6" t="inlineStr"/>
-      <c r="AH96" s="6" t="inlineStr"/>
-      <c r="AI96" s="6" t="inlineStr"/>
-      <c r="AJ96" s="6" t="inlineStr"/>
-      <c r="AK96" s="6" t="inlineStr"/>
-      <c r="AL96" s="6" t="inlineStr"/>
-      <c r="AM96" s="6" t="inlineStr"/>
-      <c r="AN96" s="6" t="inlineStr"/>
-      <c r="AO96" s="6" t="inlineStr"/>
-      <c r="AP96" s="6" t="inlineStr"/>
-      <c r="AQ96" s="6" t="inlineStr"/>
+      <c r="AB96" s="5" t="inlineStr"/>
+      <c r="AC96" s="5" t="inlineStr"/>
+      <c r="AD96" s="5" t="inlineStr"/>
+      <c r="AE96" s="5" t="inlineStr"/>
+      <c r="AF96" s="5" t="inlineStr"/>
+      <c r="AG96" s="5" t="inlineStr"/>
+      <c r="AH96" s="5" t="inlineStr"/>
+      <c r="AI96" s="5" t="inlineStr"/>
+      <c r="AJ96" s="5" t="inlineStr"/>
+      <c r="AK96" s="5" t="inlineStr"/>
+      <c r="AL96" s="5" t="inlineStr"/>
+      <c r="AM96" s="5" t="inlineStr"/>
+      <c r="AN96" s="5" t="inlineStr"/>
+      <c r="AO96" s="5" t="inlineStr"/>
+      <c r="AP96" s="5" t="inlineStr"/>
+      <c r="AQ96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -14470,81 +14486,81 @@
       <c r="AQ97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n">
+      <c r="A98" s="5" t="n">
         <v>36109560</v>
       </c>
-      <c r="B98" s="6" t="n">
+      <c r="B98" s="5" t="n">
         <v>101740241</v>
       </c>
-      <c r="C98" s="6" t="n">
+      <c r="C98" s="5" t="n">
         <v>2559898</v>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>⚠第2次住院</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G98" s="6" t="n">
+      <c r="G98" s="5" t="n">
         <v>4.71</v>
       </c>
-      <c r="H98" s="6" t="n">
+      <c r="H98" s="5" t="n">
         <v>1720</v>
       </c>
-      <c r="I98" s="6" t="inlineStr">
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>4学龄前</t>
         </is>
       </c>
-      <c r="J98" s="6" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="K98" s="6" t="n">
+      <c r="K98" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="L98" s="6" t="n">
+      <c r="L98" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="M98" s="6" t="inlineStr">
+      <c r="M98" s="5" t="inlineStr">
         <is>
           <t>胃肠外科病区</t>
         </is>
       </c>
-      <c r="N98" s="6" t="inlineStr">
+      <c r="N98" s="5" t="inlineStr">
         <is>
           <t>消化道内异物</t>
         </is>
       </c>
-      <c r="O98" s="6" t="inlineStr">
+      <c r="O98" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P98" s="6" t="inlineStr">
+      <c r="P98" s="5" t="inlineStr">
         <is>
           <t>胃穿孔 | 胃结肠瘘 | 胃内异物 | 结肠内异物</t>
         </is>
       </c>
-      <c r="Q98" s="6" t="inlineStr">
+      <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>胃穿孔、胃结肠瘘、消化道内异物(2颗异物)</t>
         </is>
       </c>
-      <c r="R98" s="6" t="inlineStr">
+      <c r="R98" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃溃疡穿孔修补术+腹腔镜下结肠瘘修补术+内镜下胃内异物去除+腹腔镜检查</t>
         </is>
       </c>
-      <c r="S98" s="6" t="inlineStr">
+      <c r="S98" s="5" t="inlineStr">
         <is>
           <t>1.取左侧卧位，麻醉成功后经口置胃镜，胃体大弯侧可见一巴克球，周围粘膜明显充血水肿，部分巴克球陷入粘膜内。考虑胃穿孔引起胃结肠内瘘形成。吸除胃内气体退出胃镜。
 2.患儿取平卧位，上尿管，手术区域常规消毒铺巾；
@@ -14553,66 +14569,66 @@
 5.告知患儿家属术中情况，家属知情同意并签字要求暂待另一粒巴克球自行排出。再次检查腹腔无明显出血及积液，术泰舒冲洗腹腔、吸尽腹腔积液后、海诺特（医用透明质酸钠凝胶）留置腹腔预防肠粘连。解除气腹，拔出各个Trocar，对合伤口皮肤，5-0可吸收线缝合5.0mm切口皮下，医用组织胶粘合，外用手术止血纱（速绫）并包扎，术毕返复苏室。术中出血约0ml，尿量约100ml。</t>
         </is>
       </c>
-      <c r="T98" s="6" t="inlineStr">
+      <c r="T98" s="5" t="inlineStr">
         <is>
           <t>2025-10-14 00:00</t>
         </is>
       </c>
-      <c r="U98" s="6" t="inlineStr">
+      <c r="U98" s="5" t="inlineStr">
         <is>
           <t>腹腔镜检查 | 腹腔镜下结肠瘘修补术 | 内镜下胃内异物去除 | 腹腔镜胃溃疡穿孔修补术</t>
         </is>
       </c>
-      <c r="V98" s="6" t="inlineStr">
+      <c r="V98" s="5" t="inlineStr">
         <is>
           <t>误食异物1月</t>
         </is>
       </c>
-      <c r="W98" s="6" t="inlineStr">
+      <c r="W98" s="5" t="inlineStr">
         <is>
           <t>1月前患儿玩耍时不慎吞食异物两枚，异物有磁性，误食后第二天有呕吐，后无特殊不适，现无发热、无恶心、无呕吐、无腹痛。未予特殊治疗，无好转。今来我院门诊就诊，以"消化道异物"收入院。        患儿自发病以来，精神食欲睡眠一般，小便正常，大便正常。</t>
         </is>
       </c>
-      <c r="X98" s="6" t="inlineStr">
+      <c r="X98" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y98" s="6" t="inlineStr">
+      <c r="Y98" s="5" t="inlineStr">
         <is>
           <t>出院情况：患儿精神食欲睡眠好，无腹痛，无呕吐，无发热，大便正常，小便正常。查体：T:36.2℃，P:110次/分，R:20次/分。神志清楚，反应可，心音有力，心律齐，呼吸平稳，双肺呼吸音清，腹部外形平坦，腹肌软，无压痛反跳痛，未见胃肠型，肠鸣音正常。伤口包扎好，敷料干燥。</t>
         </is>
       </c>
-      <c r="Z98" s="6" t="inlineStr">
+      <c r="Z98" s="5" t="inlineStr">
         <is>
           <t>误食异物1月，患者既往平时健康情况：一般，疾病史：无疾病史，外伤史：否认外伤史，过敏史：无，体温36.3℃，呼吸21次/分，规则，脉搏100次/分，规则，血压85/65mmHg，体重15.5Kg ，身长105.0cm，发育良好，营养正常，神志清楚，色泽正常，无皮疹，无水肿，浅表淋巴结无肿大，头颅形态正常，囟门闭合，眼睑正常，巩膜巩膜无黄染，瞳孔等圆等大4mm，瞳孔对光反射正常，唇红润，扁桃体双侧无肿大，咽无充血，呼吸运动两侧对称，呼吸音正常，未闻及肺部啰音，心前区无隆起，心尖搏动位置正常，心率100次/分，心律整齐，心音正常，心脏杂音未闻及，腹部外形正常，全腹柔软，无压痛，无反跳痛，肝脏肋下未触及，胆囊Murphy征阴性，脾脏肋下未触及，未触及腹部包块，移动性浊音呈阴性，肠鸣音正常，无肾区叩痛，四肢正常，，脊柱生理弯曲存在，无病理性畸形，病理反射无，Babinski征阴性。  腹部平坦，未见胃肠型；触：腹部软，全腹压痛阴性，反跳痛阴性，未扪及包块；叩：移动性浊音阴性；听：肠鸣音正常，4次/分； 我院2025-10-11 上腹部CT平扫,消化道异物（1枚位于胃内，1枚位于胃外，紧密相连），位置基本同前（2025-10-6）。我院出院小结一份。入院后完善相关检查，2025-10-13  血液分析五分类（血常规)（静脉血）:平均血小板体积 6.8(fL)↓，血小板压积 0.172(%)↓，大型血小板比率 6.2(%)↓；2025-10-13  血清肝功能11项测定:前白蛋白 187.0(mg/L)↓；2025-10-13  血清肾功能5项（BUN、Cr、UA、Cys-C、RBP)测定:尿素氮 2.60(mmol/L)↓；2025-10-13  血清电解质6项（K 、Na、Cl、Ca、Mg、P)测定:磷 1.25(mmol/L)↓；2025-10-13 窦道及瘘管造影,1.消化道不透X线异物；请结合临床进一步检查。2.所示结肠未见明显梗阻征象。于2025/10/14 全麻下行腹腔镜检查+腹腔镜胃溃疡穿孔修补术+腹腔镜下结肠瘘修补术+内镜下胃内异物去除，行抗感染、止血、补液对症等治疗。2025-10-17 胃肠道彩超,右侧腹可见数枚肠系膜淋巴结。2025-10-18  血清降钙素原(PCT)定量测定:降钙素原 0.160(ng/ml)↑；今病情稳定，临床治愈，征得家长同意，予以出院。</t>
         </is>
       </c>
-      <c r="AA98" s="6" t="inlineStr">
+      <c r="AA98" s="5" t="inlineStr">
         <is>
           <t>?1异物相关</t>
         </is>
       </c>
-      <c r="AB98" s="6" t="inlineStr">
+      <c r="AB98" s="5" t="inlineStr">
         <is>
           <t>巴克球</t>
         </is>
       </c>
-      <c r="AC98" s="6" t="inlineStr"/>
-      <c r="AD98" s="6" t="inlineStr"/>
-      <c r="AE98" s="6" t="inlineStr"/>
-      <c r="AF98" s="6" t="inlineStr"/>
-      <c r="AG98" s="6" t="inlineStr"/>
-      <c r="AH98" s="6" t="inlineStr"/>
-      <c r="AI98" s="6" t="inlineStr"/>
-      <c r="AJ98" s="6" t="inlineStr"/>
-      <c r="AK98" s="6" t="inlineStr"/>
-      <c r="AL98" s="6" t="inlineStr"/>
-      <c r="AM98" s="6" t="inlineStr"/>
-      <c r="AN98" s="6" t="inlineStr"/>
-      <c r="AO98" s="6" t="inlineStr"/>
-      <c r="AP98" s="6" t="inlineStr"/>
-      <c r="AQ98" s="6" t="inlineStr"/>
+      <c r="AC98" s="5" t="inlineStr"/>
+      <c r="AD98" s="5" t="inlineStr"/>
+      <c r="AE98" s="5" t="inlineStr"/>
+      <c r="AF98" s="5" t="inlineStr"/>
+      <c r="AG98" s="5" t="inlineStr"/>
+      <c r="AH98" s="5" t="inlineStr"/>
+      <c r="AI98" s="5" t="inlineStr"/>
+      <c r="AJ98" s="5" t="inlineStr"/>
+      <c r="AK98" s="5" t="inlineStr"/>
+      <c r="AL98" s="5" t="inlineStr"/>
+      <c r="AM98" s="5" t="inlineStr"/>
+      <c r="AN98" s="5" t="inlineStr"/>
+      <c r="AO98" s="5" t="inlineStr"/>
+      <c r="AP98" s="5" t="inlineStr"/>
+      <c r="AQ98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -15418,81 +15434,81 @@
       <c r="AQ103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="n">
+      <c r="A104" s="5" t="n">
         <v>36212580</v>
       </c>
-      <c r="B104" s="6" t="n">
+      <c r="B104" s="5" t="n">
         <v>101773423</v>
       </c>
-      <c r="C104" s="6" t="n">
+      <c r="C104" s="5" t="n">
         <v>2594168</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>⚠无出院小结</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="G104" s="6" t="n">
+      <c r="G104" s="5" t="n">
         <v>11.36</v>
       </c>
-      <c r="H104" s="6" t="n">
+      <c r="H104" s="5" t="n">
         <v>4148</v>
       </c>
-      <c r="I104" s="6" t="inlineStr">
+      <c r="I104" s="5" t="inlineStr">
         <is>
           <t>5学龄期</t>
         </is>
       </c>
-      <c r="J104" s="6" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="K104" s="6" t="n">
+      <c r="K104" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="L104" s="6" t="n">
+      <c r="L104" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="M104" s="6" t="inlineStr">
+      <c r="M104" s="5" t="inlineStr">
         <is>
           <t>肝胆外科/肿瘤外科病区</t>
         </is>
       </c>
-      <c r="N104" s="6" t="inlineStr">
+      <c r="N104" s="5" t="inlineStr">
         <is>
           <t>消化道穿孔</t>
         </is>
       </c>
-      <c r="O104" s="6" t="inlineStr">
+      <c r="O104" s="5" t="inlineStr">
         <is>
           <t>胃穿孔</t>
         </is>
       </c>
-      <c r="P104" s="6" t="inlineStr">
+      <c r="P104" s="5" t="inlineStr">
         <is>
           <t>胃穿孔 | 弥漫性腹膜炎 | 幽门螺旋杆菌感染</t>
         </is>
       </c>
-      <c r="Q104" s="6" t="inlineStr">
+      <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>胃穿孔，弥漫性腹膜炎</t>
         </is>
       </c>
-      <c r="R104" s="6" t="inlineStr">
+      <c r="R104" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃修补术+开放性胃活组织检查+经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="S104" s="6" t="inlineStr">
+      <c r="S104" s="5" t="inlineStr">
         <is>
           <t>１、平卧位，手术区域常规消毒铺巾，上导尿管顺利；
 ２、脐环左侧、右侧旁开约3cm分别作5.5ｍｍ、5.0ｍｍ切口，右肋下锁骨中线处做5.0mm切口,常规建立ＣＯ２人工气腹，压力12ｍｍＨｇ，分别置入相应大小Ｔｒｏｃａ，内置无创腹腔镜目镜、抓钳。
@@ -15501,54 +15517,54 @@
 ５、术中出血约5ml，尿量100ml，返病房。</t>
         </is>
       </c>
-      <c r="T104" s="6" t="inlineStr">
+      <c r="T104" s="5" t="inlineStr">
         <is>
           <t>2026-02-06 00:00</t>
         </is>
       </c>
-      <c r="U104" s="6" t="inlineStr">
+      <c r="U104" s="5" t="inlineStr">
         <is>
           <t>腹腔镜胃修补术 | 开放性胃活组织检查 | 经腹盆腔穿刺引流术</t>
         </is>
       </c>
-      <c r="V104" s="6" t="inlineStr">
+      <c r="V104" s="5" t="inlineStr">
         <is>
           <t>持续性上腹腹痛12小时</t>
         </is>
       </c>
-      <c r="W104" s="6" t="inlineStr">
+      <c r="W104" s="5" t="inlineStr">
         <is>
           <t>12小时前无明显诱因患儿出现持续性上腹腹痛，不伴发热，不伴呕吐，无尿频、尿急、尿痛及腰痛等不适。不洁饮食史不详，否认腹部外伤史，否认近期做过剧烈运动。曾于2026-02-05于崇阳县天城镇卫生院行腹部X线提示：腹部空腔脏器穿孔。2026-02-06于崇阳县人民医院行腹部X线提示：腹部空腔脏器穿孔。今来我院门诊就诊，以“消化道穿孔”收入院。         患儿自发病以来，精神食欲睡眠可，小便正常}，大便正常。</t>
         </is>
       </c>
-      <c r="X104" s="6" t="inlineStr">
+      <c r="X104" s="5" t="inlineStr">
         <is>
           <t>平时健康情况：一般</t>
         </is>
       </c>
-      <c r="Y104" s="6" t="inlineStr"/>
-      <c r="Z104" s="6" t="inlineStr"/>
-      <c r="AA104" s="6" t="inlineStr">
+      <c r="Y104" s="5" t="inlineStr"/>
+      <c r="Z104" s="5" t="inlineStr"/>
+      <c r="AA104" s="5" t="inlineStr">
         <is>
           <t>?3消化性溃疡</t>
         </is>
       </c>
-      <c r="AB104" s="6" t="inlineStr"/>
-      <c r="AC104" s="6" t="inlineStr"/>
-      <c r="AD104" s="6" t="inlineStr"/>
-      <c r="AE104" s="6" t="inlineStr"/>
-      <c r="AF104" s="6" t="inlineStr"/>
-      <c r="AG104" s="6" t="inlineStr"/>
-      <c r="AH104" s="6" t="inlineStr"/>
-      <c r="AI104" s="6" t="inlineStr"/>
-      <c r="AJ104" s="6" t="inlineStr"/>
-      <c r="AK104" s="6" t="inlineStr"/>
-      <c r="AL104" s="6" t="inlineStr"/>
-      <c r="AM104" s="6" t="inlineStr"/>
-      <c r="AN104" s="6" t="inlineStr"/>
-      <c r="AO104" s="6" t="inlineStr"/>
-      <c r="AP104" s="6" t="inlineStr"/>
-      <c r="AQ104" s="6" t="inlineStr"/>
+      <c r="AB104" s="5" t="inlineStr"/>
+      <c r="AC104" s="5" t="inlineStr"/>
+      <c r="AD104" s="5" t="inlineStr"/>
+      <c r="AE104" s="5" t="inlineStr"/>
+      <c r="AF104" s="5" t="inlineStr"/>
+      <c r="AG104" s="5" t="inlineStr"/>
+      <c r="AH104" s="5" t="inlineStr"/>
+      <c r="AI104" s="5" t="inlineStr"/>
+      <c r="AJ104" s="5" t="inlineStr"/>
+      <c r="AK104" s="5" t="inlineStr"/>
+      <c r="AL104" s="5" t="inlineStr"/>
+      <c r="AM104" s="5" t="inlineStr"/>
+      <c r="AN104" s="5" t="inlineStr"/>
+      <c r="AO104" s="5" t="inlineStr"/>
+      <c r="AP104" s="5" t="inlineStr"/>
+      <c r="AQ104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -16127,7 +16143,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AQ1"/>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation sqref="AC2:AC108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1异物相关,2新生儿自发性/胃壁肌层缺损,3消化性溃疡,4创伤,5医源性,6其他/特发性,9排除"</formula1>
     </dataValidation>
@@ -16149,6 +16165,9 @@
     <dataValidation sqref="AM2:AM108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"否,是"</formula1>
     </dataValidation>
+    <dataValidation sqref="AN2:AN108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"E1部位非胃十二指肠,E2无活动性穿孔,E3外院术后转入,E4同次穿孔再住院,E5资料严重缺失"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
